--- a/bjts/附录D-功能表程序血缘矩阵.xlsx
+++ b/bjts/附录D-功能表程序血缘矩阵.xlsx
@@ -16097,20 +16097,21 @@
   <dimension ref="A1:P141"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" customWidth="1"/>
-    <col min="2" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="50" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="13" max="13" width="36.453125" customWidth="1"/>
-    <col min="14" max="14" width="38.1796875" style="8" customWidth="1"/>
-    <col min="15" max="15" width="33.54296875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="38.1796875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="13" width="50" customWidth="1"/>
+    <col min="14" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="36.453125" customWidth="1"/>
     <col min="16" max="16" width="18.6328125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16124,41 +16125,41 @@
       <c r="C1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="10" t="s">
+        <v>2569</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>2570</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>2572</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>2569</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>2570</v>
       </c>
       <c r="P1" s="10" t="s">
         <v>2571</v>
@@ -16174,26 +16175,26 @@
       <c r="C2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="8" t="s">
+        <v>2417</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>2418</v>
+      </c>
+      <c r="F2" t="s">
         <v>45</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>46</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>47</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="2">
+      <c r="J2" s="2">
         <v>2</v>
-      </c>
-      <c r="I2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
       </c>
       <c r="K2" t="s">
         <v>48</v>
@@ -16201,14 +16202,14 @@
       <c r="L2" s="2">
         <v>0</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="12" t="s">
         <v>2573</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>2417</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>2418</v>
       </c>
       <c r="P2" s="8" t="s">
         <v>2419</v>
@@ -16224,20 +16225,18 @@
       <c r="C3" t="s">
         <v>50</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>46</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>48</v>
-      </c>
-      <c r="G3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -16251,13 +16250,15 @@
       <c r="L3" s="2">
         <v>0</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="12" t="s">
         <v>2574</v>
       </c>
-      <c r="N3" s="8" t="s">
-        <v>2420</v>
-      </c>
-      <c r="O3" s="8"/>
       <c r="P3" s="8" t="s">
         <v>2419</v>
       </c>
@@ -16272,20 +16273,18 @@
       <c r="C4" t="s">
         <v>53</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="8" t="s">
+        <v>2421</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" t="s">
         <v>54</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>46</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>48</v>
-      </c>
-      <c r="G4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -16299,13 +16298,15 @@
       <c r="L4" s="2">
         <v>0</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="12" t="s">
         <v>2575</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>2421</v>
-      </c>
-      <c r="O4" s="8"/>
       <c r="P4" s="8" t="s">
         <v>2419</v>
       </c>
@@ -16320,20 +16321,18 @@
       <c r="C5" t="s">
         <v>56</v>
       </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>57</v>
-      </c>
+      <c r="D5" s="8" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E5" s="8"/>
       <c r="F5" t="s">
         <v>48</v>
       </c>
       <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
         <v>48</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -16347,13 +16346,15 @@
       <c r="L5" s="2">
         <v>0</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12" t="s">
         <v>2576</v>
       </c>
-      <c r="N5" s="8" t="s">
-        <v>2422</v>
-      </c>
-      <c r="O5" s="8"/>
       <c r="P5" s="8" t="s">
         <v>2419</v>
       </c>
@@ -16368,41 +16369,41 @@
       <c r="C6" t="s">
         <v>60</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="8" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F6" t="s">
         <v>61</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>62</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>63</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="2">
+      <c r="J6" s="2">
         <v>7</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="2">
+      <c r="L6" s="2">
         <v>2</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>66</v>
       </c>
-      <c r="L6" s="2">
+      <c r="N6" s="2">
         <v>11</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="O6" s="12" t="s">
         <v>2577</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>2423</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>2424</v>
       </c>
       <c r="P6" s="8" t="s">
         <v>2425</v>
@@ -16418,41 +16419,41 @@
       <c r="C7" t="s">
         <v>69</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F7" t="s">
         <v>70</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>72</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>4</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>74</v>
-      </c>
-      <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" t="s">
-        <v>75</v>
       </c>
       <c r="L7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" t="s">
+        <v>75</v>
+      </c>
+      <c r="N7" s="2">
+        <v>5</v>
+      </c>
+      <c r="O7" s="12" t="s">
         <v>2578</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>2426</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P7" s="8" t="s">
         <v>2427</v>
@@ -16468,41 +16469,41 @@
       <c r="C8" t="s">
         <v>77</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="8" t="s">
+        <v>2428</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F8" t="s">
         <v>70</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>71</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>72</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="2">
+      <c r="J8" s="2">
         <v>4</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>74</v>
-      </c>
-      <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" t="s">
-        <v>75</v>
       </c>
       <c r="L8" s="2">
         <v>5</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" t="s">
+        <v>75</v>
+      </c>
+      <c r="N8" s="2">
+        <v>5</v>
+      </c>
+      <c r="O8" s="12" t="s">
         <v>2579</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>2428</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P8" s="8" t="s">
         <v>2427</v>
@@ -16518,41 +16519,41 @@
       <c r="C9" t="s">
         <v>79</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="8" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F9" t="s">
         <v>70</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>80</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>81</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="2">
+      <c r="J9" s="2">
         <v>2</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="2">
+      <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="2">
+      <c r="N9" s="2">
         <v>5</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="O9" s="12" t="s">
         <v>2580</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>2429</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P9" s="8" t="s">
         <v>2427</v>
@@ -16568,41 +16569,41 @@
       <c r="C10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="8" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F10" t="s">
         <v>70</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>80</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>85</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="2">
+      <c r="J10" s="2">
         <v>3</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>87</v>
       </c>
-      <c r="J10" s="2">
+      <c r="L10" s="2">
         <v>4</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="2">
+      <c r="N10" s="2">
         <v>5</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="O10" s="12" t="s">
         <v>2581</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>2430</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P10" s="8" t="s">
         <v>2427</v>
@@ -16618,41 +16619,41 @@
       <c r="C11" t="s">
         <v>89</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="8" t="s">
+        <v>2431</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F11" t="s">
         <v>70</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>80</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>90</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="2">
+      <c r="J11" s="2">
         <v>3</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="2">
+      <c r="L11" s="2">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="2">
+      <c r="N11" s="2">
         <v>5</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="O11" s="12" t="s">
         <v>2582</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>2431</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P11" s="8" t="s">
         <v>2427</v>
@@ -16668,41 +16669,41 @@
       <c r="C12" t="s">
         <v>95</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="8" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F12" t="s">
         <v>70</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>96</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>97</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="2">
+      <c r="J12" s="2">
         <v>1</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="2">
+      <c r="L12" s="2">
         <v>0</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>99</v>
       </c>
-      <c r="L12" s="2">
+      <c r="N12" s="2">
         <v>1</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="O12" s="12" t="s">
         <v>2583</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>2432</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P12" s="8" t="s">
         <v>2427</v>
@@ -16718,41 +16719,41 @@
       <c r="C13" t="s">
         <v>101</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="8" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F13" t="s">
         <v>70</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>80</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>102</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="2">
+      <c r="J13" s="2">
         <v>2</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="2">
+      <c r="L13" s="2">
         <v>0</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>99</v>
       </c>
-      <c r="L13" s="2">
+      <c r="N13" s="2">
         <v>1</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="O13" s="12" t="s">
         <v>2584</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>2433</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>2427</v>
@@ -16768,26 +16769,26 @@
       <c r="C14" t="s">
         <v>106</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="8" t="s">
+        <v>2434</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F14" t="s">
         <v>70</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>107</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>108</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="2">
+      <c r="J14" s="2">
         <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
       </c>
       <c r="K14" t="s">
         <v>48</v>
@@ -16795,14 +16796,14 @@
       <c r="L14" s="2">
         <v>0</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14" s="12" t="s">
         <v>2585</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>2434</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>2427</v>
@@ -16818,26 +16819,26 @@
       <c r="C15" t="s">
         <v>111</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="8" t="s">
+        <v>2435</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F15" t="s">
         <v>70</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>112</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>108</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>109</v>
       </c>
-      <c r="H15" s="2">
+      <c r="J15" s="2">
         <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
       </c>
       <c r="K15" t="s">
         <v>48</v>
@@ -16845,14 +16846,14 @@
       <c r="L15" s="2">
         <v>0</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="M15" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="s">
         <v>2586</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>2435</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>2436</v>
@@ -16868,26 +16869,26 @@
       <c r="C16" t="s">
         <v>114</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="8" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>115</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>108</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="2">
+      <c r="J16" s="2">
         <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0</v>
       </c>
       <c r="K16" t="s">
         <v>48</v>
@@ -16895,14 +16896,14 @@
       <c r="L16" s="2">
         <v>0</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" s="12" t="s">
         <v>2587</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>2437</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P16" s="8" t="s">
         <v>2438</v>
@@ -16918,26 +16919,26 @@
       <c r="C17" t="s">
         <v>117</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="8" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>118</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>119</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="2">
+      <c r="J17" s="2">
         <v>1</v>
-      </c>
-      <c r="I17" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
       </c>
       <c r="K17" t="s">
         <v>48</v>
@@ -16945,14 +16946,14 @@
       <c r="L17" s="2">
         <v>0</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12" t="s">
         <v>2588</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>2439</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P17" s="8" t="s">
         <v>2440</v>
@@ -16968,41 +16969,41 @@
       <c r="C18" t="s">
         <v>123</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="8" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F18" t="s">
         <v>70</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>71</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>97</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="2">
+      <c r="J18" s="2">
         <v>1</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="2">
+      <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="K18" t="s">
+      <c r="M18" t="s">
         <v>99</v>
       </c>
-      <c r="L18" s="2">
+      <c r="N18" s="2">
         <v>1</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="O18" s="12" t="s">
         <v>2589</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>2441</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>2427</v>
@@ -17018,41 +17019,41 @@
       <c r="C19" t="s">
         <v>125</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="8" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F19" t="s">
         <v>70</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>71</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>97</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="2">
+      <c r="J19" s="2">
         <v>2</v>
       </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="2">
+      <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" t="s">
         <v>75</v>
       </c>
-      <c r="L19" s="2">
+      <c r="N19" s="2">
         <v>5</v>
       </c>
-      <c r="M19" s="12" t="s">
+      <c r="O19" s="12" t="s">
         <v>2590</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>2442</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P19" s="8" t="s">
         <v>2427</v>
@@ -17068,41 +17069,41 @@
       <c r="C20" t="s">
         <v>128</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="8" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F20" t="s">
         <v>70</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>71</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>97</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>98</v>
       </c>
-      <c r="H20" s="2">
+      <c r="J20" s="2">
         <v>1</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="2">
+      <c r="L20" s="2">
         <v>0</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>99</v>
       </c>
-      <c r="L20" s="2">
+      <c r="N20" s="2">
         <v>1</v>
       </c>
-      <c r="M20" s="12" t="s">
+      <c r="O20" s="12" t="s">
         <v>2591</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>2443</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P20" s="8" t="s">
         <v>2427</v>
@@ -17118,41 +17119,41 @@
       <c r="C21" t="s">
         <v>130</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="8" t="s">
+        <v>2444</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F21" t="s">
         <v>70</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>71</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>131</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>132</v>
-      </c>
-      <c r="H21" s="2">
-        <v>4</v>
-      </c>
-      <c r="I21" t="s">
-        <v>87</v>
       </c>
       <c r="J21" s="2">
         <v>4</v>
       </c>
       <c r="K21" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="2">
+        <v>4</v>
+      </c>
+      <c r="M21" t="s">
         <v>99</v>
       </c>
-      <c r="L21" s="2">
+      <c r="N21" s="2">
         <v>1</v>
       </c>
-      <c r="M21" s="12" t="s">
+      <c r="O21" s="12" t="s">
         <v>2592</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>2444</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>2403</v>
       </c>
       <c r="P21" s="8" t="s">
         <v>2427</v>
@@ -17168,41 +17169,41 @@
       <c r="C22" t="s">
         <v>135</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="8" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F22" t="s">
         <v>136</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>80</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>137</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>138</v>
       </c>
-      <c r="H22" s="2">
+      <c r="J22" s="2">
         <v>5</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>48</v>
       </c>
-      <c r="J22" s="2">
+      <c r="L22" s="2">
         <v>0</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>139</v>
       </c>
-      <c r="L22" s="2">
+      <c r="N22" s="2">
         <v>9</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="O22" s="12" t="s">
         <v>2593</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>2445</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>2446</v>
       </c>
       <c r="P22" s="8" t="s">
         <v>2447</v>
@@ -17218,41 +17219,41 @@
       <c r="C23" t="s">
         <v>141</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="8" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F23" t="s">
         <v>136</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>80</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>137</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>138</v>
       </c>
-      <c r="H23" s="2">
+      <c r="J23" s="2">
         <v>5</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="2">
+      <c r="L23" s="2">
         <v>0</v>
       </c>
-      <c r="K23" t="s">
+      <c r="M23" t="s">
         <v>139</v>
       </c>
-      <c r="L23" s="2">
+      <c r="N23" s="2">
         <v>9</v>
       </c>
-      <c r="M23" s="12" t="s">
+      <c r="O23" s="12" t="s">
         <v>2594</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>2448</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>2446</v>
       </c>
       <c r="P23" s="8" t="s">
         <v>2447</v>
@@ -17268,41 +17269,41 @@
       <c r="C24" t="s">
         <v>143</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="8" t="s">
+        <v>2449</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F24" t="s">
         <v>136</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>71</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>144</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>145</v>
       </c>
-      <c r="H24" s="2">
+      <c r="J24" s="2">
         <v>3</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>146</v>
       </c>
-      <c r="J24" s="2">
+      <c r="L24" s="2">
         <v>5</v>
       </c>
-      <c r="K24" t="s">
+      <c r="M24" t="s">
         <v>147</v>
       </c>
-      <c r="L24" s="2">
+      <c r="N24" s="2">
         <v>9</v>
       </c>
-      <c r="M24" s="12" t="s">
+      <c r="O24" s="12" t="s">
         <v>2595</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>2449</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>2446</v>
       </c>
       <c r="P24" s="8" t="s">
         <v>2425</v>
@@ -17318,41 +17319,41 @@
       <c r="C25" t="s">
         <v>149</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="8" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F25" t="s">
         <v>136</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>150</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>151</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>152</v>
       </c>
-      <c r="H25" s="2">
+      <c r="J25" s="2">
         <v>2</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>48</v>
       </c>
-      <c r="J25" s="2">
+      <c r="L25" s="2">
         <v>0</v>
       </c>
-      <c r="K25" t="s">
+      <c r="M25" t="s">
         <v>153</v>
       </c>
-      <c r="L25" s="2">
+      <c r="N25" s="2">
         <v>7</v>
       </c>
-      <c r="M25" s="12" t="s">
+      <c r="O25" s="12" t="s">
         <v>2596</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>2450</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>2446</v>
       </c>
       <c r="P25" s="8" t="s">
         <v>2409</v>
@@ -17368,41 +17369,41 @@
       <c r="C26" t="s">
         <v>155</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="8" t="s">
+        <v>2451</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F26" t="s">
         <v>136</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>80</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>156</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>157</v>
       </c>
-      <c r="H26" s="2">
+      <c r="J26" s="2">
         <v>2</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>48</v>
       </c>
-      <c r="J26" s="2">
+      <c r="L26" s="2">
         <v>0</v>
       </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
         <v>158</v>
       </c>
-      <c r="L26" s="2">
+      <c r="N26" s="2">
         <v>8</v>
       </c>
-      <c r="M26" s="12" t="s">
+      <c r="O26" s="12" t="s">
         <v>2597</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>2451</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>2446</v>
       </c>
       <c r="P26" s="8" t="s">
         <v>2409</v>
@@ -17418,26 +17419,26 @@
       <c r="C27" t="s">
         <v>161</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="8" t="s">
+        <v>2452</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F27" t="s">
         <v>136</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>112</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H27" t="s">
         <v>162</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
         <v>163</v>
       </c>
-      <c r="H27" s="2">
+      <c r="J27" s="2">
         <v>1</v>
-      </c>
-      <c r="I27" t="s">
-        <v>48</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0</v>
       </c>
       <c r="K27" t="s">
         <v>48</v>
@@ -17445,14 +17446,14 @@
       <c r="L27" s="2">
         <v>0</v>
       </c>
-      <c r="M27" s="12" t="s">
+      <c r="M27" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="s">
         <v>2598</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>2452</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P27" s="8" t="s">
         <v>2453</v>
@@ -17468,26 +17469,26 @@
       <c r="C28" t="s">
         <v>165</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="8" t="s">
+        <v>2454</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F28" t="s">
         <v>136</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>80</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>162</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>163</v>
       </c>
-      <c r="H28" s="2">
+      <c r="J28" s="2">
         <v>1</v>
-      </c>
-      <c r="I28" t="s">
-        <v>48</v>
-      </c>
-      <c r="J28" s="2">
-        <v>0</v>
       </c>
       <c r="K28" t="s">
         <v>48</v>
@@ -17495,14 +17496,14 @@
       <c r="L28" s="2">
         <v>0</v>
       </c>
-      <c r="M28" s="12" t="s">
+      <c r="M28" t="s">
+        <v>48</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="12" t="s">
         <v>2599</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>2454</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P28" s="8" t="s">
         <v>2425</v>
@@ -17518,41 +17519,41 @@
       <c r="C29" t="s">
         <v>168</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="8" t="s">
+        <v>2455</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F29" t="s">
         <v>136</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>80</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
         <v>169</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>170</v>
       </c>
-      <c r="H29" s="2">
+      <c r="J29" s="2">
         <v>2</v>
       </c>
-      <c r="I29" t="s">
+      <c r="K29" t="s">
         <v>171</v>
-      </c>
-      <c r="J29" s="2">
-        <v>5</v>
-      </c>
-      <c r="K29" t="s">
-        <v>75</v>
       </c>
       <c r="L29" s="2">
         <v>5</v>
       </c>
-      <c r="M29" s="12" t="s">
+      <c r="M29" t="s">
+        <v>75</v>
+      </c>
+      <c r="N29" s="2">
+        <v>5</v>
+      </c>
+      <c r="O29" s="12" t="s">
         <v>2600</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>2455</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P29" s="8" t="s">
         <v>2425</v>
@@ -17568,41 +17569,41 @@
       <c r="C30" t="s">
         <v>174</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="8" t="s">
+        <v>2456</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F30" t="s">
         <v>175</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>176</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
         <v>177</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
         <v>178</v>
       </c>
-      <c r="H30" s="2">
+      <c r="J30" s="2">
         <v>2</v>
       </c>
-      <c r="I30" t="s">
+      <c r="K30" t="s">
         <v>179</v>
       </c>
-      <c r="J30" s="2">
+      <c r="L30" s="2">
         <v>3</v>
       </c>
-      <c r="K30" t="s">
+      <c r="M30" t="s">
         <v>180</v>
       </c>
-      <c r="L30" s="2">
+      <c r="N30" s="2">
         <v>4</v>
       </c>
-      <c r="M30" s="12" t="s">
+      <c r="O30" s="12" t="s">
         <v>2601</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P30" s="8" t="s">
         <v>2453</v>
@@ -17618,41 +17619,41 @@
       <c r="C31" t="s">
         <v>182</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="8" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F31" t="s">
         <v>175</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>183</v>
       </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
         <v>184</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
         <v>185</v>
       </c>
-      <c r="H31" s="2">
+      <c r="J31" s="2">
         <v>2</v>
       </c>
-      <c r="I31" t="s">
+      <c r="K31" t="s">
         <v>186</v>
       </c>
-      <c r="J31" s="2">
+      <c r="L31" s="2">
         <v>5</v>
       </c>
-      <c r="K31" t="s">
+      <c r="M31" t="s">
         <v>187</v>
       </c>
-      <c r="L31" s="2">
+      <c r="N31" s="2">
         <v>4</v>
       </c>
-      <c r="M31" s="12" t="s">
+      <c r="O31" s="12" t="s">
         <v>2602</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>2457</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P31" s="8" t="s">
         <v>2425</v>
@@ -17668,41 +17669,41 @@
       <c r="C32" t="s">
         <v>189</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="8" t="s">
+        <v>2458</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F32" t="s">
         <v>175</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>183</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>184</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
         <v>185</v>
       </c>
-      <c r="H32" s="2">
+      <c r="J32" s="2">
         <v>2</v>
       </c>
-      <c r="I32" t="s">
+      <c r="K32" t="s">
         <v>186</v>
       </c>
-      <c r="J32" s="2">
+      <c r="L32" s="2">
         <v>5</v>
       </c>
-      <c r="K32" t="s">
+      <c r="M32" t="s">
         <v>187</v>
       </c>
-      <c r="L32" s="2">
+      <c r="N32" s="2">
         <v>4</v>
       </c>
-      <c r="M32" s="12" t="s">
+      <c r="O32" s="12" t="s">
         <v>2602</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>2458</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P32" s="8" t="s">
         <v>2425</v>
@@ -17718,41 +17719,41 @@
       <c r="C33" t="s">
         <v>191</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="8" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F33" t="s">
         <v>175</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>183</v>
       </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>184</v>
       </c>
-      <c r="G33" t="s">
+      <c r="I33" t="s">
         <v>185</v>
       </c>
-      <c r="H33" s="2">
+      <c r="J33" s="2">
         <v>2</v>
       </c>
-      <c r="I33" t="s">
+      <c r="K33" t="s">
         <v>186</v>
       </c>
-      <c r="J33" s="2">
+      <c r="L33" s="2">
         <v>5</v>
       </c>
-      <c r="K33" t="s">
+      <c r="M33" t="s">
         <v>187</v>
       </c>
-      <c r="L33" s="2">
+      <c r="N33" s="2">
         <v>4</v>
       </c>
-      <c r="M33" s="12" t="s">
+      <c r="O33" s="12" t="s">
         <v>2602</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>2459</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P33" s="8" t="s">
         <v>2425</v>
@@ -17768,41 +17769,41 @@
       <c r="C34" t="s">
         <v>193</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="8" t="s">
+        <v>2460</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F34" t="s">
         <v>175</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>183</v>
       </c>
-      <c r="F34" t="s">
+      <c r="H34" t="s">
         <v>184</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
         <v>185</v>
       </c>
-      <c r="H34" s="2">
+      <c r="J34" s="2">
         <v>2</v>
       </c>
-      <c r="I34" t="s">
+      <c r="K34" t="s">
         <v>186</v>
       </c>
-      <c r="J34" s="2">
+      <c r="L34" s="2">
         <v>5</v>
       </c>
-      <c r="K34" t="s">
+      <c r="M34" t="s">
         <v>187</v>
       </c>
-      <c r="L34" s="2">
+      <c r="N34" s="2">
         <v>4</v>
       </c>
-      <c r="M34" s="12" t="s">
+      <c r="O34" s="12" t="s">
         <v>2603</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>2460</v>
-      </c>
-      <c r="O34" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P34" s="8" t="s">
         <v>2419</v>
@@ -17818,41 +17819,41 @@
       <c r="C35" t="s">
         <v>195</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="8" t="s">
+        <v>2461</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F35" t="s">
         <v>175</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>183</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>184</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" t="s">
         <v>185</v>
       </c>
-      <c r="H35" s="2">
+      <c r="J35" s="2">
         <v>2</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
         <v>186</v>
       </c>
-      <c r="J35" s="2">
+      <c r="L35" s="2">
         <v>5</v>
       </c>
-      <c r="K35" t="s">
+      <c r="M35" t="s">
         <v>187</v>
       </c>
-      <c r="L35" s="2">
+      <c r="N35" s="2">
         <v>4</v>
       </c>
-      <c r="M35" s="12" t="s">
+      <c r="O35" s="12" t="s">
         <v>2603</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>2461</v>
-      </c>
-      <c r="O35" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P35" s="8" t="s">
         <v>2419</v>
@@ -17868,41 +17869,41 @@
       <c r="C36" t="s">
         <v>197</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="8" t="s">
+        <v>2462</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F36" t="s">
         <v>175</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>183</v>
       </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>184</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36" t="s">
         <v>185</v>
       </c>
-      <c r="H36" s="2">
+      <c r="J36" s="2">
         <v>2</v>
       </c>
-      <c r="I36" t="s">
+      <c r="K36" t="s">
         <v>186</v>
       </c>
-      <c r="J36" s="2">
+      <c r="L36" s="2">
         <v>5</v>
       </c>
-      <c r="K36" t="s">
+      <c r="M36" t="s">
         <v>187</v>
       </c>
-      <c r="L36" s="2">
+      <c r="N36" s="2">
         <v>4</v>
       </c>
-      <c r="M36" s="12" t="s">
+      <c r="O36" s="12" t="s">
         <v>2603</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>2462</v>
-      </c>
-      <c r="O36" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P36" s="8" t="s">
         <v>2419</v>
@@ -17918,41 +17919,41 @@
       <c r="C37" t="s">
         <v>199</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="8" t="s">
+        <v>2463</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F37" t="s">
         <v>175</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>183</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>184</v>
       </c>
-      <c r="G37" t="s">
+      <c r="I37" t="s">
         <v>185</v>
       </c>
-      <c r="H37" s="2">
+      <c r="J37" s="2">
         <v>2</v>
       </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>186</v>
       </c>
-      <c r="J37" s="2">
+      <c r="L37" s="2">
         <v>5</v>
       </c>
-      <c r="K37" t="s">
+      <c r="M37" t="s">
         <v>187</v>
       </c>
-      <c r="L37" s="2">
+      <c r="N37" s="2">
         <v>4</v>
       </c>
-      <c r="M37" s="12" t="s">
+      <c r="O37" s="12" t="s">
         <v>2603</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>2463</v>
-      </c>
-      <c r="O37" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P37" s="8" t="s">
         <v>2419</v>
@@ -17968,40 +17969,40 @@
       <c r="C38" t="s">
         <v>201</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="8" t="s">
+        <v>2464</v>
+      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" t="s">
         <v>175</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>183</v>
       </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
         <v>177</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>178</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>2</v>
       </c>
-      <c r="I38" t="s">
+      <c r="K38" t="s">
         <v>179</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>3</v>
       </c>
-      <c r="K38" t="s">
+      <c r="M38" t="s">
         <v>180</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>4</v>
       </c>
-      <c r="M38" s="12" t="s">
+      <c r="O38" s="12" t="s">
         <v>2604</v>
       </c>
-      <c r="N38" s="8" t="s">
-        <v>2464</v>
-      </c>
-      <c r="O38" s="8"/>
       <c r="P38" s="8" t="s">
         <v>2465</v>
       </c>
@@ -18016,41 +18017,41 @@
       <c r="C39" t="s">
         <v>204</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="8" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F39" t="s">
         <v>175</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>205</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" t="s">
         <v>206</v>
       </c>
-      <c r="G39" t="s">
+      <c r="I39" t="s">
         <v>207</v>
       </c>
-      <c r="H39" s="2">
+      <c r="J39" s="2">
         <v>6</v>
       </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>208</v>
       </c>
-      <c r="J39" s="2">
+      <c r="L39" s="2">
         <v>5</v>
       </c>
-      <c r="K39" t="s">
+      <c r="M39" t="s">
         <v>209</v>
       </c>
-      <c r="L39" s="2">
+      <c r="N39" s="2">
         <v>2</v>
       </c>
-      <c r="M39" s="12" t="s">
+      <c r="O39" s="12" t="s">
         <v>2605</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>2466</v>
-      </c>
-      <c r="O39" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P39" s="8" t="s">
         <v>2425</v>
@@ -18066,41 +18067,41 @@
       <c r="C40" t="s">
         <v>211</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="8" t="s">
+        <v>2467</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F40" t="s">
         <v>175</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>80</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" t="s">
         <v>212</v>
       </c>
-      <c r="G40" t="s">
+      <c r="I40" t="s">
         <v>213</v>
       </c>
-      <c r="H40" s="2">
+      <c r="J40" s="2">
         <v>3</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>208</v>
       </c>
-      <c r="J40" s="2">
+      <c r="L40" s="2">
         <v>5</v>
       </c>
-      <c r="K40" t="s">
+      <c r="M40" t="s">
         <v>209</v>
       </c>
-      <c r="L40" s="2">
+      <c r="N40" s="2">
         <v>2</v>
       </c>
-      <c r="M40" s="12" t="s">
+      <c r="O40" s="12" t="s">
         <v>2606</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>2467</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P40" s="8" t="s">
         <v>2425</v>
@@ -18116,41 +18117,41 @@
       <c r="C41" t="s">
         <v>215</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="8" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F41" t="s">
         <v>175</v>
       </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>71</v>
       </c>
-      <c r="F41" t="s">
+      <c r="H41" t="s">
         <v>216</v>
       </c>
-      <c r="G41" t="s">
+      <c r="I41" t="s">
         <v>217</v>
-      </c>
-      <c r="H41" s="2">
-        <v>5</v>
-      </c>
-      <c r="I41" t="s">
-        <v>208</v>
       </c>
       <c r="J41" s="2">
         <v>5</v>
       </c>
       <c r="K41" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L41" s="2">
         <v>5</v>
       </c>
-      <c r="M41" s="12" t="s">
+      <c r="M41" t="s">
+        <v>75</v>
+      </c>
+      <c r="N41" s="2">
+        <v>5</v>
+      </c>
+      <c r="O41" s="12" t="s">
         <v>2607</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>2468</v>
-      </c>
-      <c r="O41" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P41" s="8" t="s">
         <v>2425</v>
@@ -18166,41 +18167,41 @@
       <c r="C42" t="s">
         <v>219</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="8" t="s">
+        <v>2469</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F42" t="s">
         <v>175</v>
       </c>
-      <c r="E42" t="s">
+      <c r="G42" t="s">
         <v>71</v>
       </c>
-      <c r="F42" t="s">
+      <c r="H42" t="s">
         <v>220</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" t="s">
         <v>221</v>
-      </c>
-      <c r="H42" s="2">
-        <v>5</v>
-      </c>
-      <c r="I42" t="s">
-        <v>208</v>
       </c>
       <c r="J42" s="2">
         <v>5</v>
       </c>
       <c r="K42" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L42" s="2">
         <v>5</v>
       </c>
-      <c r="M42" s="12" t="s">
+      <c r="M42" t="s">
+        <v>75</v>
+      </c>
+      <c r="N42" s="2">
+        <v>5</v>
+      </c>
+      <c r="O42" s="12" t="s">
         <v>2608</v>
-      </c>
-      <c r="N42" s="8" t="s">
-        <v>2469</v>
-      </c>
-      <c r="O42" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P42" s="8" t="s">
         <v>2425</v>
@@ -18216,41 +18217,41 @@
       <c r="C43" t="s">
         <v>223</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="8" t="s">
+        <v>2470</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F43" t="s">
         <v>175</v>
       </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>112</v>
       </c>
-      <c r="F43" t="s">
+      <c r="H43" t="s">
         <v>224</v>
       </c>
-      <c r="G43" t="s">
+      <c r="I43" t="s">
         <v>225</v>
-      </c>
-      <c r="H43" s="2">
-        <v>5</v>
-      </c>
-      <c r="I43" t="s">
-        <v>208</v>
       </c>
       <c r="J43" s="2">
         <v>5</v>
       </c>
       <c r="K43" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L43" s="2">
         <v>5</v>
       </c>
-      <c r="M43" s="12" t="s">
+      <c r="M43" t="s">
+        <v>75</v>
+      </c>
+      <c r="N43" s="2">
+        <v>5</v>
+      </c>
+      <c r="O43" s="12" t="s">
         <v>2609</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>2470</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P43" s="8" t="s">
         <v>2425</v>
@@ -18266,41 +18267,41 @@
       <c r="C44" t="s">
         <v>227</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="8" t="s">
+        <v>2471</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F44" t="s">
         <v>175</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>71</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" t="s">
         <v>228</v>
       </c>
-      <c r="G44" t="s">
+      <c r="I44" t="s">
         <v>229</v>
-      </c>
-      <c r="H44" s="2">
-        <v>5</v>
-      </c>
-      <c r="I44" t="s">
-        <v>208</v>
       </c>
       <c r="J44" s="2">
         <v>5</v>
       </c>
       <c r="K44" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L44" s="2">
         <v>5</v>
       </c>
-      <c r="M44" s="12" t="s">
+      <c r="M44" t="s">
+        <v>75</v>
+      </c>
+      <c r="N44" s="2">
+        <v>5</v>
+      </c>
+      <c r="O44" s="12" t="s">
         <v>2610</v>
-      </c>
-      <c r="N44" s="8" t="s">
-        <v>2471</v>
-      </c>
-      <c r="O44" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P44" s="8" t="s">
         <v>2425</v>
@@ -18316,41 +18317,41 @@
       <c r="C45" t="s">
         <v>231</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="8" t="s">
+        <v>2472</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F45" t="s">
         <v>175</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>71</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" t="s">
         <v>232</v>
       </c>
-      <c r="G45" t="s">
+      <c r="I45" t="s">
         <v>233</v>
-      </c>
-      <c r="H45" s="2">
-        <v>5</v>
-      </c>
-      <c r="I45" t="s">
-        <v>208</v>
       </c>
       <c r="J45" s="2">
         <v>5</v>
       </c>
       <c r="K45" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L45" s="2">
         <v>5</v>
       </c>
-      <c r="M45" s="12" t="s">
+      <c r="M45" t="s">
+        <v>75</v>
+      </c>
+      <c r="N45" s="2">
+        <v>5</v>
+      </c>
+      <c r="O45" s="12" t="s">
         <v>2611</v>
-      </c>
-      <c r="N45" s="8" t="s">
-        <v>2472</v>
-      </c>
-      <c r="O45" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P45" s="8" t="s">
         <v>2425</v>
@@ -18366,41 +18367,41 @@
       <c r="C46" t="s">
         <v>235</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="8" t="s">
+        <v>2473</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F46" t="s">
         <v>175</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>71</v>
       </c>
-      <c r="F46" t="s">
+      <c r="H46" t="s">
         <v>236</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" t="s">
         <v>237</v>
-      </c>
-      <c r="H46" s="2">
-        <v>5</v>
-      </c>
-      <c r="I46" t="s">
-        <v>208</v>
       </c>
       <c r="J46" s="2">
         <v>5</v>
       </c>
       <c r="K46" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L46" s="2">
         <v>5</v>
       </c>
-      <c r="M46" s="12" t="s">
+      <c r="M46" t="s">
+        <v>75</v>
+      </c>
+      <c r="N46" s="2">
+        <v>5</v>
+      </c>
+      <c r="O46" s="12" t="s">
         <v>2612</v>
-      </c>
-      <c r="N46" s="8" t="s">
-        <v>2473</v>
-      </c>
-      <c r="O46" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P46" s="8" t="s">
         <v>2425</v>
@@ -18416,41 +18417,41 @@
       <c r="C47" t="s">
         <v>239</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="8" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F47" t="s">
         <v>175</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>71</v>
       </c>
-      <c r="F47" t="s">
+      <c r="H47" t="s">
         <v>240</v>
       </c>
-      <c r="G47" t="s">
+      <c r="I47" t="s">
         <v>241</v>
-      </c>
-      <c r="H47" s="2">
-        <v>5</v>
-      </c>
-      <c r="I47" t="s">
-        <v>208</v>
       </c>
       <c r="J47" s="2">
         <v>5</v>
       </c>
       <c r="K47" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L47" s="2">
         <v>5</v>
       </c>
-      <c r="M47" s="12" t="s">
+      <c r="M47" t="s">
+        <v>75</v>
+      </c>
+      <c r="N47" s="2">
+        <v>5</v>
+      </c>
+      <c r="O47" s="12" t="s">
         <v>2613</v>
-      </c>
-      <c r="N47" s="8" t="s">
-        <v>2474</v>
-      </c>
-      <c r="O47" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P47" s="8" t="s">
         <v>2425</v>
@@ -18466,41 +18467,41 @@
       <c r="C48" t="s">
         <v>243</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="8" t="s">
+        <v>2475</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F48" t="s">
         <v>175</v>
       </c>
-      <c r="E48" t="s">
+      <c r="G48" t="s">
         <v>71</v>
       </c>
-      <c r="F48" t="s">
+      <c r="H48" t="s">
         <v>244</v>
       </c>
-      <c r="G48" t="s">
+      <c r="I48" t="s">
         <v>245</v>
       </c>
-      <c r="H48" s="2">
+      <c r="J48" s="2">
         <v>3</v>
       </c>
-      <c r="I48" t="s">
+      <c r="K48" t="s">
         <v>246</v>
-      </c>
-      <c r="J48" s="2">
-        <v>5</v>
-      </c>
-      <c r="K48" t="s">
-        <v>75</v>
       </c>
       <c r="L48" s="2">
         <v>5</v>
       </c>
-      <c r="M48" s="12" t="s">
+      <c r="M48" t="s">
+        <v>75</v>
+      </c>
+      <c r="N48" s="2">
+        <v>5</v>
+      </c>
+      <c r="O48" s="12" t="s">
         <v>2614</v>
-      </c>
-      <c r="N48" s="8" t="s">
-        <v>2475</v>
-      </c>
-      <c r="O48" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P48" s="8" t="s">
         <v>2425</v>
@@ -18516,41 +18517,41 @@
       <c r="C49" t="s">
         <v>248</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="8" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F49" t="s">
         <v>175</v>
       </c>
-      <c r="E49" t="s">
+      <c r="G49" t="s">
         <v>71</v>
       </c>
-      <c r="F49" t="s">
+      <c r="H49" t="s">
         <v>249</v>
       </c>
-      <c r="G49" t="s">
+      <c r="I49" t="s">
         <v>250</v>
       </c>
-      <c r="H49" s="2">
+      <c r="J49" s="2">
         <v>1</v>
       </c>
-      <c r="I49" t="s">
+      <c r="K49" t="s">
         <v>48</v>
       </c>
-      <c r="J49" s="2">
+      <c r="L49" s="2">
         <v>0</v>
       </c>
-      <c r="K49" t="s">
+      <c r="M49" t="s">
         <v>251</v>
       </c>
-      <c r="L49" s="2">
+      <c r="N49" s="2">
         <v>2</v>
       </c>
-      <c r="M49" s="12" t="s">
+      <c r="O49" s="12" t="s">
         <v>2615</v>
-      </c>
-      <c r="N49" s="8" t="s">
-        <v>2476</v>
-      </c>
-      <c r="O49" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P49" s="8" t="s">
         <v>2453</v>
@@ -18566,41 +18567,41 @@
       <c r="C50" t="s">
         <v>254</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="8" t="s">
+        <v>2477</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F50" t="s">
         <v>175</v>
       </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>57</v>
       </c>
-      <c r="F50" t="s">
+      <c r="H50" t="s">
         <v>255</v>
       </c>
-      <c r="G50" t="s">
+      <c r="I50" t="s">
         <v>256</v>
       </c>
-      <c r="H50" s="2">
+      <c r="J50" s="2">
         <v>2</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>48</v>
       </c>
-      <c r="J50" s="2">
+      <c r="L50" s="2">
         <v>0</v>
       </c>
-      <c r="K50" t="s">
+      <c r="M50" t="s">
         <v>257</v>
       </c>
-      <c r="L50" s="2">
+      <c r="N50" s="2">
         <v>4</v>
       </c>
-      <c r="M50" s="12" t="s">
+      <c r="O50" s="12" t="s">
         <v>2616</v>
-      </c>
-      <c r="N50" s="8" t="s">
-        <v>2477</v>
-      </c>
-      <c r="O50" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P50" s="8" t="s">
         <v>2410</v>
@@ -18616,41 +18617,41 @@
       <c r="C51" t="s">
         <v>259</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="8" t="s">
+        <v>2479</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F51" t="s">
         <v>175</v>
       </c>
-      <c r="E51" t="s">
+      <c r="G51" t="s">
         <v>71</v>
       </c>
-      <c r="F51" t="s">
+      <c r="H51" t="s">
         <v>260</v>
       </c>
-      <c r="G51" t="s">
+      <c r="I51" t="s">
         <v>261</v>
-      </c>
-      <c r="H51" s="2">
-        <v>2</v>
-      </c>
-      <c r="I51" t="s">
-        <v>262</v>
       </c>
       <c r="J51" s="2">
         <v>2</v>
       </c>
       <c r="K51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L51" s="2">
         <v>2</v>
       </c>
-      <c r="M51" s="12" t="s">
+      <c r="M51" t="s">
+        <v>263</v>
+      </c>
+      <c r="N51" s="2">
+        <v>2</v>
+      </c>
+      <c r="O51" s="12" t="s">
         <v>2617</v>
-      </c>
-      <c r="N51" s="8" t="s">
-        <v>2479</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P51" s="8" t="s">
         <v>2410</v>
@@ -18666,41 +18667,41 @@
       <c r="C52" t="s">
         <v>265</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="8" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F52" t="s">
         <v>175</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>71</v>
       </c>
-      <c r="F52" t="s">
+      <c r="H52" t="s">
         <v>255</v>
       </c>
-      <c r="G52" t="s">
+      <c r="I52" t="s">
         <v>256</v>
       </c>
-      <c r="H52" s="2">
+      <c r="J52" s="2">
         <v>2</v>
       </c>
-      <c r="I52" t="s">
+      <c r="K52" t="s">
         <v>48</v>
       </c>
-      <c r="J52" s="2">
+      <c r="L52" s="2">
         <v>0</v>
       </c>
-      <c r="K52" t="s">
+      <c r="M52" t="s">
         <v>257</v>
       </c>
-      <c r="L52" s="2">
+      <c r="N52" s="2">
         <v>4</v>
       </c>
-      <c r="M52" s="12" t="s">
+      <c r="O52" s="12" t="s">
         <v>2618</v>
-      </c>
-      <c r="N52" s="8" t="s">
-        <v>2480</v>
-      </c>
-      <c r="O52" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P52" s="8" t="s">
         <v>2410</v>
@@ -18716,41 +18717,41 @@
       <c r="C53" t="s">
         <v>267</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="8" t="s">
+        <v>2481</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F53" t="s">
         <v>175</v>
       </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>71</v>
       </c>
-      <c r="F53" t="s">
+      <c r="H53" t="s">
         <v>255</v>
       </c>
-      <c r="G53" t="s">
+      <c r="I53" t="s">
         <v>256</v>
       </c>
-      <c r="H53" s="2">
+      <c r="J53" s="2">
         <v>2</v>
       </c>
-      <c r="I53" t="s">
+      <c r="K53" t="s">
         <v>48</v>
       </c>
-      <c r="J53" s="2">
+      <c r="L53" s="2">
         <v>0</v>
       </c>
-      <c r="K53" t="s">
+      <c r="M53" t="s">
         <v>257</v>
       </c>
-      <c r="L53" s="2">
+      <c r="N53" s="2">
         <v>4</v>
       </c>
-      <c r="M53" s="12" t="s">
+      <c r="O53" s="12" t="s">
         <v>2619</v>
-      </c>
-      <c r="N53" s="8" t="s">
-        <v>2481</v>
-      </c>
-      <c r="O53" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P53" s="8" t="s">
         <v>2410</v>
@@ -18766,41 +18767,41 @@
       <c r="C54" t="s">
         <v>269</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="8" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F54" t="s">
         <v>175</v>
       </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>57</v>
       </c>
-      <c r="F54" t="s">
+      <c r="H54" t="s">
         <v>255</v>
       </c>
-      <c r="G54" t="s">
+      <c r="I54" t="s">
         <v>256</v>
       </c>
-      <c r="H54" s="2">
+      <c r="J54" s="2">
         <v>2</v>
       </c>
-      <c r="I54" t="s">
+      <c r="K54" t="s">
         <v>48</v>
       </c>
-      <c r="J54" s="2">
+      <c r="L54" s="2">
         <v>0</v>
       </c>
-      <c r="K54" t="s">
+      <c r="M54" t="s">
         <v>257</v>
       </c>
-      <c r="L54" s="2">
+      <c r="N54" s="2">
         <v>4</v>
       </c>
-      <c r="M54" s="12" t="s">
+      <c r="O54" s="12" t="s">
         <v>2620</v>
-      </c>
-      <c r="N54" s="8" t="s">
-        <v>2482</v>
-      </c>
-      <c r="O54" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P54" s="8" t="s">
         <v>2410</v>
@@ -18816,41 +18817,41 @@
       <c r="C55" t="s">
         <v>271</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="8" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F55" t="s">
         <v>175</v>
       </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>57</v>
       </c>
-      <c r="F55" t="s">
+      <c r="H55" t="s">
         <v>255</v>
       </c>
-      <c r="G55" t="s">
+      <c r="I55" t="s">
         <v>256</v>
       </c>
-      <c r="H55" s="2">
+      <c r="J55" s="2">
         <v>2</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" t="s">
         <v>48</v>
       </c>
-      <c r="J55" s="2">
+      <c r="L55" s="2">
         <v>0</v>
       </c>
-      <c r="K55" t="s">
+      <c r="M55" t="s">
         <v>257</v>
       </c>
-      <c r="L55" s="2">
+      <c r="N55" s="2">
         <v>4</v>
       </c>
-      <c r="M55" s="12" t="s">
+      <c r="O55" s="12" t="s">
         <v>2621</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>2483</v>
-      </c>
-      <c r="O55" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P55" s="8" t="s">
         <v>2410</v>
@@ -18866,41 +18867,41 @@
       <c r="C56" t="s">
         <v>273</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="8" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F56" t="s">
         <v>175</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>80</v>
       </c>
-      <c r="F56" t="s">
+      <c r="H56" t="s">
         <v>274</v>
       </c>
-      <c r="G56" t="s">
+      <c r="I56" t="s">
         <v>275</v>
       </c>
-      <c r="H56" s="2">
+      <c r="J56" s="2">
         <v>1</v>
       </c>
-      <c r="I56" t="s">
+      <c r="K56" t="s">
         <v>48</v>
       </c>
-      <c r="J56" s="2">
+      <c r="L56" s="2">
         <v>0</v>
       </c>
-      <c r="K56" t="s">
+      <c r="M56" t="s">
         <v>276</v>
       </c>
-      <c r="L56" s="2">
+      <c r="N56" s="2">
         <v>1</v>
       </c>
-      <c r="M56" s="12" t="s">
+      <c r="O56" s="12" t="s">
         <v>2622</v>
-      </c>
-      <c r="N56" s="8" t="s">
-        <v>2484</v>
-      </c>
-      <c r="O56" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P56" s="8" t="s">
         <v>2410</v>
@@ -18916,41 +18917,41 @@
       <c r="C57" t="s">
         <v>278</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="8" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F57" t="s">
         <v>175</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>205</v>
       </c>
-      <c r="F57" t="s">
+      <c r="H57" t="s">
         <v>279</v>
       </c>
-      <c r="G57" t="s">
+      <c r="I57" t="s">
         <v>280</v>
       </c>
-      <c r="H57" s="2">
+      <c r="J57" s="2">
         <v>2</v>
       </c>
-      <c r="I57" t="s">
+      <c r="K57" t="s">
         <v>48</v>
       </c>
-      <c r="J57" s="2">
+      <c r="L57" s="2">
         <v>0</v>
       </c>
-      <c r="K57" t="s">
+      <c r="M57" t="s">
         <v>281</v>
       </c>
-      <c r="L57" s="2">
+      <c r="N57" s="2">
         <v>3</v>
       </c>
-      <c r="M57" s="12" t="s">
+      <c r="O57" s="12" t="s">
         <v>2623</v>
-      </c>
-      <c r="N57" s="8" t="s">
-        <v>2485</v>
-      </c>
-      <c r="O57" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="P57" s="8" t="s">
         <v>2410</v>
@@ -18966,26 +18967,26 @@
       <c r="C58" t="s">
         <v>284</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="8" t="s">
+        <v>2486</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F58" t="s">
         <v>136</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>285</v>
       </c>
-      <c r="F58" t="s">
+      <c r="H58" t="s">
         <v>286</v>
       </c>
-      <c r="G58" t="s">
+      <c r="I58" t="s">
         <v>287</v>
       </c>
-      <c r="H58" s="2">
+      <c r="J58" s="2">
         <v>4</v>
-      </c>
-      <c r="I58" t="s">
-        <v>48</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0</v>
       </c>
       <c r="K58" t="s">
         <v>48</v>
@@ -18993,14 +18994,14 @@
       <c r="L58" s="2">
         <v>0</v>
       </c>
-      <c r="M58" s="12" t="s">
+      <c r="M58" t="s">
+        <v>48</v>
+      </c>
+      <c r="N58" s="2">
+        <v>0</v>
+      </c>
+      <c r="O58" s="12" t="s">
         <v>2624</v>
-      </c>
-      <c r="N58" s="8" t="s">
-        <v>2486</v>
-      </c>
-      <c r="O58" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P58" s="8" t="s">
         <v>2453</v>
@@ -19016,26 +19017,26 @@
       <c r="C59" t="s">
         <v>289</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="8" t="s">
+        <v>2487</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F59" t="s">
         <v>136</v>
       </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>96</v>
       </c>
-      <c r="F59" t="s">
+      <c r="H59" t="s">
         <v>290</v>
       </c>
-      <c r="G59" t="s">
+      <c r="I59" t="s">
         <v>291</v>
       </c>
-      <c r="H59" s="2">
+      <c r="J59" s="2">
         <v>2</v>
-      </c>
-      <c r="I59" t="s">
-        <v>48</v>
-      </c>
-      <c r="J59" s="2">
-        <v>0</v>
       </c>
       <c r="K59" t="s">
         <v>48</v>
@@ -19043,14 +19044,14 @@
       <c r="L59" s="2">
         <v>0</v>
       </c>
-      <c r="M59" s="12" t="s">
+      <c r="M59" t="s">
+        <v>48</v>
+      </c>
+      <c r="N59" s="2">
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="s">
         <v>2625</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>2487</v>
-      </c>
-      <c r="O59" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P59" s="8" t="s">
         <v>2453</v>
@@ -19066,26 +19067,26 @@
       <c r="C60" t="s">
         <v>293</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="8" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F60" t="s">
         <v>136</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>150</v>
       </c>
-      <c r="F60" t="s">
+      <c r="H60" t="s">
         <v>290</v>
       </c>
-      <c r="G60" t="s">
+      <c r="I60" t="s">
         <v>291</v>
       </c>
-      <c r="H60" s="2">
+      <c r="J60" s="2">
         <v>2</v>
-      </c>
-      <c r="I60" t="s">
-        <v>48</v>
-      </c>
-      <c r="J60" s="2">
-        <v>0</v>
       </c>
       <c r="K60" t="s">
         <v>48</v>
@@ -19093,14 +19094,14 @@
       <c r="L60" s="2">
         <v>0</v>
       </c>
-      <c r="M60" s="12" t="s">
+      <c r="M60" t="s">
+        <v>48</v>
+      </c>
+      <c r="N60" s="2">
+        <v>0</v>
+      </c>
+      <c r="O60" s="12" t="s">
         <v>2626</v>
-      </c>
-      <c r="N60" s="8" t="s">
-        <v>2488</v>
-      </c>
-      <c r="O60" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P60" s="8" t="s">
         <v>2453</v>
@@ -19116,20 +19117,20 @@
       <c r="C61" t="s">
         <v>296</v>
       </c>
-      <c r="D61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" t="s">
-        <v>150</v>
+      <c r="D61" s="8" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>2490</v>
       </c>
       <c r="F61" t="s">
         <v>48</v>
       </c>
       <c r="G61" t="s">
+        <v>150</v>
+      </c>
+      <c r="H61" t="s">
         <v>48</v>
-      </c>
-      <c r="H61" s="2">
-        <v>0</v>
       </c>
       <c r="I61" t="s">
         <v>48</v>
@@ -19143,14 +19144,14 @@
       <c r="L61" s="2">
         <v>0</v>
       </c>
-      <c r="M61" s="12" t="s">
+      <c r="M61" t="s">
+        <v>48</v>
+      </c>
+      <c r="N61" s="2">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="s">
         <v>2627</v>
-      </c>
-      <c r="N61" s="8" t="s">
-        <v>2489</v>
-      </c>
-      <c r="O61" s="8" t="s">
-        <v>2490</v>
       </c>
       <c r="P61" s="8" t="s">
         <v>2453</v>
@@ -19166,41 +19167,41 @@
       <c r="C62" t="s">
         <v>299</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="8" t="s">
+        <v>2491</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F62" t="s">
         <v>136</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>285</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" t="s">
         <v>300</v>
       </c>
-      <c r="G62" t="s">
+      <c r="I62" t="s">
         <v>301</v>
       </c>
-      <c r="H62" s="2">
+      <c r="J62" s="2">
         <v>3</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>302</v>
       </c>
-      <c r="J62" s="2">
+      <c r="L62" s="2">
         <v>5</v>
       </c>
-      <c r="K62" t="s">
+      <c r="M62" t="s">
         <v>303</v>
       </c>
-      <c r="L62" s="2">
+      <c r="N62" s="2">
         <v>10</v>
       </c>
-      <c r="M62" s="12" t="s">
+      <c r="O62" s="12" t="s">
         <v>2628</v>
-      </c>
-      <c r="N62" s="8" t="s">
-        <v>2491</v>
-      </c>
-      <c r="O62" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P62" s="8" t="s">
         <v>2453</v>
@@ -19216,41 +19217,41 @@
       <c r="C63" t="s">
         <v>306</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="8" t="s">
+        <v>2492</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F63" t="s">
         <v>136</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>80</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" t="s">
         <v>307</v>
       </c>
-      <c r="G63" t="s">
+      <c r="I63" t="s">
         <v>308</v>
       </c>
-      <c r="H63" s="2">
+      <c r="J63" s="2">
         <v>2</v>
       </c>
-      <c r="I63" t="s">
+      <c r="K63" t="s">
         <v>48</v>
       </c>
-      <c r="J63" s="2">
+      <c r="L63" s="2">
         <v>0</v>
       </c>
-      <c r="K63" t="s">
+      <c r="M63" t="s">
         <v>75</v>
       </c>
-      <c r="L63" s="2">
+      <c r="N63" s="2">
         <v>5</v>
       </c>
-      <c r="M63" s="12" t="s">
+      <c r="O63" s="12" t="s">
         <v>2629</v>
-      </c>
-      <c r="N63" s="8" t="s">
-        <v>2492</v>
-      </c>
-      <c r="O63" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P63" s="8" t="s">
         <v>2425</v>
@@ -19266,41 +19267,41 @@
       <c r="C64" t="s">
         <v>311</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="8" t="s">
+        <v>2493</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F64" t="s">
         <v>61</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>80</v>
       </c>
-      <c r="F64" t="s">
+      <c r="H64" t="s">
         <v>312</v>
       </c>
-      <c r="G64" t="s">
+      <c r="I64" t="s">
         <v>313</v>
       </c>
-      <c r="H64" s="2">
+      <c r="J64" s="2">
         <v>5</v>
       </c>
-      <c r="I64" t="s">
+      <c r="K64" t="s">
         <v>87</v>
       </c>
-      <c r="J64" s="2">
+      <c r="L64" s="2">
         <v>4</v>
       </c>
-      <c r="K64" t="s">
+      <c r="M64" t="s">
         <v>314</v>
       </c>
-      <c r="L64" s="2">
+      <c r="N64" s="2">
         <v>11</v>
       </c>
-      <c r="M64" s="12" t="s">
+      <c r="O64" s="12" t="s">
         <v>2630</v>
-      </c>
-      <c r="N64" s="8" t="s">
-        <v>2493</v>
-      </c>
-      <c r="O64" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P64" s="8" t="s">
         <v>2425</v>
@@ -19316,41 +19317,41 @@
       <c r="C65" t="s">
         <v>316</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="8" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F65" t="s">
         <v>61</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>80</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" t="s">
         <v>312</v>
       </c>
-      <c r="G65" t="s">
+      <c r="I65" t="s">
         <v>313</v>
       </c>
-      <c r="H65" s="2">
+      <c r="J65" s="2">
         <v>5</v>
       </c>
-      <c r="I65" t="s">
+      <c r="K65" t="s">
         <v>87</v>
       </c>
-      <c r="J65" s="2">
+      <c r="L65" s="2">
         <v>4</v>
       </c>
-      <c r="K65" t="s">
+      <c r="M65" t="s">
         <v>314</v>
       </c>
-      <c r="L65" s="2">
+      <c r="N65" s="2">
         <v>11</v>
       </c>
-      <c r="M65" s="12" t="s">
+      <c r="O65" s="12" t="s">
         <v>2631</v>
-      </c>
-      <c r="N65" s="8" t="s">
-        <v>2494</v>
-      </c>
-      <c r="O65" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P65" s="8" t="s">
         <v>2425</v>
@@ -19366,41 +19367,41 @@
       <c r="C66" t="s">
         <v>318</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="8" t="s">
+        <v>2495</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F66" t="s">
         <v>61</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>80</v>
       </c>
-      <c r="F66" t="s">
+      <c r="H66" t="s">
         <v>312</v>
       </c>
-      <c r="G66" t="s">
+      <c r="I66" t="s">
         <v>313</v>
       </c>
-      <c r="H66" s="2">
+      <c r="J66" s="2">
         <v>5</v>
       </c>
-      <c r="I66" t="s">
+      <c r="K66" t="s">
         <v>87</v>
       </c>
-      <c r="J66" s="2">
+      <c r="L66" s="2">
         <v>4</v>
       </c>
-      <c r="K66" t="s">
+      <c r="M66" t="s">
         <v>314</v>
       </c>
-      <c r="L66" s="2">
+      <c r="N66" s="2">
         <v>11</v>
       </c>
-      <c r="M66" s="12" t="s">
+      <c r="O66" s="12" t="s">
         <v>2632</v>
-      </c>
-      <c r="N66" s="8" t="s">
-        <v>2495</v>
-      </c>
-      <c r="O66" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P66" s="8" t="s">
         <v>2425</v>
@@ -19416,41 +19417,41 @@
       <c r="C67" t="s">
         <v>320</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="8" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F67" t="s">
         <v>61</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>80</v>
       </c>
-      <c r="F67" t="s">
+      <c r="H67" t="s">
         <v>312</v>
       </c>
-      <c r="G67" t="s">
+      <c r="I67" t="s">
         <v>313</v>
       </c>
-      <c r="H67" s="2">
+      <c r="J67" s="2">
         <v>5</v>
       </c>
-      <c r="I67" t="s">
+      <c r="K67" t="s">
         <v>87</v>
       </c>
-      <c r="J67" s="2">
+      <c r="L67" s="2">
         <v>4</v>
       </c>
-      <c r="K67" t="s">
+      <c r="M67" t="s">
         <v>314</v>
       </c>
-      <c r="L67" s="2">
+      <c r="N67" s="2">
         <v>11</v>
       </c>
-      <c r="M67" s="12" t="s">
+      <c r="O67" s="12" t="s">
         <v>2633</v>
-      </c>
-      <c r="N67" s="8" t="s">
-        <v>2496</v>
-      </c>
-      <c r="O67" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P67" s="8" t="s">
         <v>2425</v>
@@ -19466,41 +19467,41 @@
       <c r="C68" t="s">
         <v>322</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="8" t="s">
+        <v>2497</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F68" t="s">
         <v>61</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>80</v>
       </c>
-      <c r="F68" t="s">
+      <c r="H68" t="s">
         <v>312</v>
       </c>
-      <c r="G68" t="s">
+      <c r="I68" t="s">
         <v>313</v>
       </c>
-      <c r="H68" s="2">
+      <c r="J68" s="2">
         <v>5</v>
       </c>
-      <c r="I68" t="s">
+      <c r="K68" t="s">
         <v>87</v>
       </c>
-      <c r="J68" s="2">
+      <c r="L68" s="2">
         <v>4</v>
       </c>
-      <c r="K68" t="s">
+      <c r="M68" t="s">
         <v>314</v>
       </c>
-      <c r="L68" s="2">
+      <c r="N68" s="2">
         <v>11</v>
       </c>
-      <c r="M68" s="12" t="s">
+      <c r="O68" s="12" t="s">
         <v>2634</v>
-      </c>
-      <c r="N68" s="8" t="s">
-        <v>2497</v>
-      </c>
-      <c r="O68" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P68" s="8" t="s">
         <v>2425</v>
@@ -19516,41 +19517,41 @@
       <c r="C69" t="s">
         <v>324</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="8" t="s">
+        <v>2498</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F69" t="s">
         <v>61</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>80</v>
       </c>
-      <c r="F69" t="s">
+      <c r="H69" t="s">
         <v>325</v>
       </c>
-      <c r="G69" t="s">
+      <c r="I69" t="s">
         <v>326</v>
       </c>
-      <c r="H69" s="2">
+      <c r="J69" s="2">
         <v>6</v>
       </c>
-      <c r="I69" t="s">
+      <c r="K69" t="s">
         <v>327</v>
       </c>
-      <c r="J69" s="2">
+      <c r="L69" s="2">
         <v>3</v>
       </c>
-      <c r="K69" t="s">
+      <c r="M69" t="s">
         <v>328</v>
       </c>
-      <c r="L69" s="2">
+      <c r="N69" s="2">
         <v>2</v>
       </c>
-      <c r="M69" s="12" t="s">
+      <c r="O69" s="12" t="s">
         <v>2635</v>
-      </c>
-      <c r="N69" s="8" t="s">
-        <v>2498</v>
-      </c>
-      <c r="O69" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P69" s="8" t="s">
         <v>2425</v>
@@ -19566,41 +19567,41 @@
       <c r="C70" t="s">
         <v>330</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="8" t="s">
+        <v>2499</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F70" t="s">
         <v>61</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
         <v>80</v>
       </c>
-      <c r="F70" t="s">
+      <c r="H70" t="s">
         <v>331</v>
       </c>
-      <c r="G70" t="s">
+      <c r="I70" t="s">
         <v>332</v>
       </c>
-      <c r="H70" s="2">
+      <c r="J70" s="2">
         <v>8</v>
       </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>333</v>
       </c>
-      <c r="J70" s="2">
+      <c r="L70" s="2">
         <v>1</v>
       </c>
-      <c r="K70" t="s">
+      <c r="M70" t="s">
         <v>328</v>
       </c>
-      <c r="L70" s="2">
+      <c r="N70" s="2">
         <v>2</v>
       </c>
-      <c r="M70" s="12" t="s">
+      <c r="O70" s="12" t="s">
         <v>2636</v>
-      </c>
-      <c r="N70" s="8" t="s">
-        <v>2499</v>
-      </c>
-      <c r="O70" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P70" s="8" t="s">
         <v>2425</v>
@@ -19616,41 +19617,41 @@
       <c r="C71" t="s">
         <v>336</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="8" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F71" t="s">
         <v>61</v>
       </c>
-      <c r="E71" t="s">
+      <c r="G71" t="s">
         <v>80</v>
       </c>
-      <c r="F71" t="s">
+      <c r="H71" t="s">
         <v>337</v>
       </c>
-      <c r="G71" t="s">
+      <c r="I71" t="s">
         <v>338</v>
-      </c>
-      <c r="H71" s="2">
-        <v>5</v>
-      </c>
-      <c r="I71" t="s">
-        <v>339</v>
       </c>
       <c r="J71" s="2">
         <v>5</v>
       </c>
       <c r="K71" t="s">
+        <v>339</v>
+      </c>
+      <c r="L71" s="2">
+        <v>5</v>
+      </c>
+      <c r="M71" t="s">
         <v>340</v>
       </c>
-      <c r="L71" s="2">
+      <c r="N71" s="2">
         <v>7</v>
       </c>
-      <c r="M71" s="12" t="s">
+      <c r="O71" s="12" t="s">
         <v>2637</v>
-      </c>
-      <c r="N71" s="8" t="s">
-        <v>2500</v>
-      </c>
-      <c r="O71" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P71" s="8" t="s">
         <v>2425</v>
@@ -19666,41 +19667,41 @@
       <c r="C72" t="s">
         <v>343</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="8" t="s">
+        <v>2501</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F72" t="s">
         <v>61</v>
       </c>
-      <c r="E72" t="s">
+      <c r="G72" t="s">
         <v>80</v>
       </c>
-      <c r="F72" t="s">
+      <c r="H72" t="s">
         <v>344</v>
       </c>
-      <c r="G72" t="s">
+      <c r="I72" t="s">
         <v>345</v>
-      </c>
-      <c r="H72" s="2">
-        <v>5</v>
-      </c>
-      <c r="I72" t="s">
-        <v>171</v>
       </c>
       <c r="J72" s="2">
         <v>5</v>
       </c>
       <c r="K72" t="s">
+        <v>171</v>
+      </c>
+      <c r="L72" s="2">
+        <v>5</v>
+      </c>
+      <c r="M72" t="s">
         <v>346</v>
       </c>
-      <c r="L72" s="2">
+      <c r="N72" s="2">
         <v>7</v>
       </c>
-      <c r="M72" s="12" t="s">
+      <c r="O72" s="12" t="s">
         <v>2638</v>
-      </c>
-      <c r="N72" s="8" t="s">
-        <v>2501</v>
-      </c>
-      <c r="O72" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P72" s="8" t="s">
         <v>2425</v>
@@ -19716,41 +19717,41 @@
       <c r="C73" t="s">
         <v>348</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="8" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F73" t="s">
         <v>61</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>80</v>
       </c>
-      <c r="F73" t="s">
+      <c r="H73" t="s">
         <v>349</v>
       </c>
-      <c r="G73" t="s">
+      <c r="I73" t="s">
         <v>350</v>
       </c>
-      <c r="H73" s="2">
+      <c r="J73" s="2">
         <v>7</v>
       </c>
-      <c r="I73" t="s">
+      <c r="K73" t="s">
         <v>351</v>
-      </c>
-      <c r="J73" s="2">
-        <v>2</v>
-      </c>
-      <c r="K73" t="s">
-        <v>328</v>
       </c>
       <c r="L73" s="2">
         <v>2</v>
       </c>
-      <c r="M73" s="12" t="s">
+      <c r="M73" t="s">
+        <v>328</v>
+      </c>
+      <c r="N73" s="2">
+        <v>2</v>
+      </c>
+      <c r="O73" s="12" t="s">
         <v>2639</v>
-      </c>
-      <c r="N73" s="8" t="s">
-        <v>2502</v>
-      </c>
-      <c r="O73" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P73" s="8" t="s">
         <v>2425</v>
@@ -19766,41 +19767,41 @@
       <c r="C74" t="s">
         <v>353</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="8" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F74" t="s">
         <v>61</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>80</v>
       </c>
-      <c r="F74" t="s">
+      <c r="H74" t="s">
         <v>354</v>
       </c>
-      <c r="G74" t="s">
+      <c r="I74" t="s">
         <v>355</v>
       </c>
-      <c r="H74" s="2">
+      <c r="J74" s="2">
         <v>11</v>
       </c>
-      <c r="I74" t="s">
+      <c r="K74" t="s">
         <v>356</v>
       </c>
-      <c r="J74" s="2">
+      <c r="L74" s="2">
         <v>5</v>
       </c>
-      <c r="K74" t="s">
+      <c r="M74" t="s">
         <v>328</v>
       </c>
-      <c r="L74" s="2">
+      <c r="N74" s="2">
         <v>2</v>
       </c>
-      <c r="M74" s="12" t="s">
+      <c r="O74" s="12" t="s">
         <v>2640</v>
-      </c>
-      <c r="N74" s="8" t="s">
-        <v>2503</v>
-      </c>
-      <c r="O74" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P74" s="8" t="s">
         <v>2425</v>
@@ -19816,41 +19817,41 @@
       <c r="C75" t="s">
         <v>358</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="8" t="s">
+        <v>2504</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F75" t="s">
         <v>61</v>
       </c>
-      <c r="E75" t="s">
+      <c r="G75" t="s">
         <v>80</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" t="s">
         <v>359</v>
       </c>
-      <c r="G75" t="s">
+      <c r="I75" t="s">
         <v>360</v>
-      </c>
-      <c r="H75" s="2">
-        <v>5</v>
-      </c>
-      <c r="I75" t="s">
-        <v>361</v>
       </c>
       <c r="J75" s="2">
         <v>5</v>
       </c>
       <c r="K75" t="s">
+        <v>361</v>
+      </c>
+      <c r="L75" s="2">
+        <v>5</v>
+      </c>
+      <c r="M75" t="s">
         <v>362</v>
       </c>
-      <c r="L75" s="2">
+      <c r="N75" s="2">
         <v>1</v>
       </c>
-      <c r="M75" s="12" t="s">
+      <c r="O75" s="12" t="s">
         <v>2641</v>
-      </c>
-      <c r="N75" s="8" t="s">
-        <v>2504</v>
-      </c>
-      <c r="O75" s="8" t="s">
-        <v>2404</v>
       </c>
       <c r="P75" s="8" t="s">
         <v>2425</v>
@@ -19866,41 +19867,41 @@
       <c r="C76" t="s">
         <v>365</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="8" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F76" t="s">
         <v>175</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>80</v>
       </c>
-      <c r="F76" t="s">
+      <c r="H76" t="s">
         <v>366</v>
       </c>
-      <c r="G76" t="s">
+      <c r="I76" t="s">
         <v>367</v>
       </c>
-      <c r="H76" s="2">
+      <c r="J76" s="2">
         <v>7</v>
       </c>
-      <c r="I76" t="s">
+      <c r="K76" t="s">
         <v>368</v>
       </c>
-      <c r="J76" s="2">
+      <c r="L76" s="2">
         <v>5</v>
       </c>
-      <c r="K76" t="s">
+      <c r="M76" t="s">
         <v>369</v>
       </c>
-      <c r="L76" s="2">
+      <c r="N76" s="2">
         <v>15</v>
       </c>
-      <c r="M76" s="12" t="s">
+      <c r="O76" s="12" t="s">
         <v>2642</v>
-      </c>
-      <c r="N76" s="8" t="s">
-        <v>2505</v>
-      </c>
-      <c r="O76" s="8" t="s">
-        <v>2405</v>
       </c>
       <c r="P76" s="8" t="s">
         <v>2425</v>
@@ -19916,41 +19917,41 @@
       <c r="C77" t="s">
         <v>371</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="8" t="s">
+        <v>2506</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F77" t="s">
         <v>175</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
         <v>112</v>
       </c>
-      <c r="F77" t="s">
+      <c r="H77" t="s">
         <v>372</v>
       </c>
-      <c r="G77" t="s">
+      <c r="I77" t="s">
         <v>373</v>
       </c>
-      <c r="H77" s="2">
+      <c r="J77" s="2">
         <v>8</v>
       </c>
-      <c r="I77" t="s">
+      <c r="K77" t="s">
         <v>368</v>
       </c>
-      <c r="J77" s="2">
+      <c r="L77" s="2">
         <v>5</v>
       </c>
-      <c r="K77" t="s">
+      <c r="M77" t="s">
         <v>369</v>
       </c>
-      <c r="L77" s="2">
+      <c r="N77" s="2">
         <v>15</v>
       </c>
-      <c r="M77" s="12" t="s">
+      <c r="O77" s="12" t="s">
         <v>2643</v>
-      </c>
-      <c r="N77" s="8" t="s">
-        <v>2506</v>
-      </c>
-      <c r="O77" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P77" s="8" t="s">
         <v>2453</v>
@@ -19966,41 +19967,41 @@
       <c r="C78" t="s">
         <v>375</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="8" t="s">
+        <v>2508</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F78" t="s">
         <v>175</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>96</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" t="s">
         <v>376</v>
       </c>
-      <c r="G78" t="s">
+      <c r="I78" t="s">
         <v>377</v>
       </c>
-      <c r="H78" s="2">
+      <c r="J78" s="2">
         <v>6</v>
       </c>
-      <c r="I78" t="s">
+      <c r="K78" t="s">
         <v>48</v>
       </c>
-      <c r="J78" s="2">
+      <c r="L78" s="2">
         <v>0</v>
       </c>
-      <c r="K78" t="s">
+      <c r="M78" t="s">
         <v>378</v>
       </c>
-      <c r="L78" s="2">
+      <c r="N78" s="2">
         <v>9</v>
       </c>
-      <c r="M78" s="12" t="s">
+      <c r="O78" s="12" t="s">
         <v>2644</v>
-      </c>
-      <c r="N78" s="8" t="s">
-        <v>2508</v>
-      </c>
-      <c r="O78" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P78" s="8" t="s">
         <v>2453</v>
@@ -20016,41 +20017,41 @@
       <c r="C79" t="s">
         <v>381</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="8" t="s">
+        <v>2509</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F79" t="s">
         <v>175</v>
       </c>
-      <c r="E79" t="s">
+      <c r="G79" t="s">
         <v>150</v>
       </c>
-      <c r="F79" t="s">
+      <c r="H79" t="s">
         <v>382</v>
       </c>
-      <c r="G79" t="s">
+      <c r="I79" t="s">
         <v>383</v>
       </c>
-      <c r="H79" s="2">
+      <c r="J79" s="2">
         <v>3</v>
       </c>
-      <c r="I79" t="s">
+      <c r="K79" t="s">
         <v>48</v>
       </c>
-      <c r="J79" s="2">
+      <c r="L79" s="2">
         <v>0</v>
       </c>
-      <c r="K79" t="s">
+      <c r="M79" t="s">
         <v>384</v>
       </c>
-      <c r="L79" s="2">
+      <c r="N79" s="2">
         <v>4</v>
       </c>
-      <c r="M79" s="12" t="s">
+      <c r="O79" s="12" t="s">
         <v>2645</v>
-      </c>
-      <c r="N79" s="8" t="s">
-        <v>2509</v>
-      </c>
-      <c r="O79" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P79" s="8" t="s">
         <v>2453</v>
@@ -20066,41 +20067,41 @@
       <c r="C80" t="s">
         <v>386</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="8" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F80" t="s">
         <v>175</v>
       </c>
-      <c r="E80" t="s">
+      <c r="G80" t="s">
         <v>150</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" t="s">
         <v>387</v>
       </c>
-      <c r="G80" t="s">
+      <c r="I80" t="s">
         <v>388</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>3</v>
       </c>
-      <c r="I80" t="s">
+      <c r="K80" t="s">
         <v>48</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>0</v>
       </c>
-      <c r="K80" t="s">
+      <c r="M80" t="s">
         <v>389</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>4</v>
       </c>
-      <c r="M80" s="12" t="s">
+      <c r="O80" s="12" t="s">
         <v>2646</v>
-      </c>
-      <c r="N80" s="8" t="s">
-        <v>2510</v>
-      </c>
-      <c r="O80" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P80" s="8" t="s">
         <v>2453</v>
@@ -20116,41 +20117,41 @@
       <c r="C81" t="s">
         <v>391</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="8" t="s">
+        <v>2511</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F81" t="s">
         <v>175</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>150</v>
       </c>
-      <c r="F81" t="s">
+      <c r="H81" t="s">
         <v>392</v>
       </c>
-      <c r="G81" t="s">
+      <c r="I81" t="s">
         <v>393</v>
       </c>
-      <c r="H81" s="2">
+      <c r="J81" s="2">
         <v>3</v>
       </c>
-      <c r="I81" t="s">
+      <c r="K81" t="s">
         <v>48</v>
       </c>
-      <c r="J81" s="2">
+      <c r="L81" s="2">
         <v>0</v>
       </c>
-      <c r="K81" t="s">
+      <c r="M81" t="s">
         <v>394</v>
       </c>
-      <c r="L81" s="2">
+      <c r="N81" s="2">
         <v>4</v>
       </c>
-      <c r="M81" s="12" t="s">
+      <c r="O81" s="12" t="s">
         <v>2647</v>
-      </c>
-      <c r="N81" s="8" t="s">
-        <v>2511</v>
-      </c>
-      <c r="O81" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P81" s="8" t="s">
         <v>2453</v>
@@ -20166,41 +20167,41 @@
       <c r="C82" t="s">
         <v>396</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="8" t="s">
+        <v>2512</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F82" t="s">
         <v>175</v>
       </c>
-      <c r="E82" t="s">
+      <c r="G82" t="s">
         <v>150</v>
       </c>
-      <c r="F82" t="s">
+      <c r="H82" t="s">
         <v>397</v>
       </c>
-      <c r="G82" t="s">
+      <c r="I82" t="s">
         <v>398</v>
       </c>
-      <c r="H82" s="2">
+      <c r="J82" s="2">
         <v>3</v>
       </c>
-      <c r="I82" t="s">
+      <c r="K82" t="s">
         <v>48</v>
       </c>
-      <c r="J82" s="2">
+      <c r="L82" s="2">
         <v>0</v>
       </c>
-      <c r="K82" t="s">
+      <c r="M82" t="s">
         <v>399</v>
       </c>
-      <c r="L82" s="2">
+      <c r="N82" s="2">
         <v>4</v>
       </c>
-      <c r="M82" s="12" t="s">
+      <c r="O82" s="12" t="s">
         <v>2648</v>
-      </c>
-      <c r="N82" s="8" t="s">
-        <v>2512</v>
-      </c>
-      <c r="O82" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P82" s="8" t="s">
         <v>2453</v>
@@ -20216,41 +20217,41 @@
       <c r="C83" t="s">
         <v>401</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="8" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F83" t="s">
         <v>175</v>
       </c>
-      <c r="E83" t="s">
+      <c r="G83" t="s">
         <v>150</v>
       </c>
-      <c r="F83" t="s">
+      <c r="H83" t="s">
         <v>402</v>
       </c>
-      <c r="G83" t="s">
+      <c r="I83" t="s">
         <v>403</v>
       </c>
-      <c r="H83" s="2">
+      <c r="J83" s="2">
         <v>3</v>
       </c>
-      <c r="I83" t="s">
+      <c r="K83" t="s">
         <v>48</v>
       </c>
-      <c r="J83" s="2">
+      <c r="L83" s="2">
         <v>0</v>
       </c>
-      <c r="K83" t="s">
+      <c r="M83" t="s">
         <v>404</v>
       </c>
-      <c r="L83" s="2">
+      <c r="N83" s="2">
         <v>4</v>
       </c>
-      <c r="M83" s="12" t="s">
+      <c r="O83" s="12" t="s">
         <v>2649</v>
-      </c>
-      <c r="N83" s="8" t="s">
-        <v>2513</v>
-      </c>
-      <c r="O83" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P83" s="8" t="s">
         <v>2453</v>
@@ -20266,41 +20267,41 @@
       <c r="C84" t="s">
         <v>406</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="8" t="s">
+        <v>2514</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F84" t="s">
         <v>175</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>150</v>
       </c>
-      <c r="F84" t="s">
+      <c r="H84" t="s">
         <v>407</v>
       </c>
-      <c r="G84" t="s">
+      <c r="I84" t="s">
         <v>408</v>
       </c>
-      <c r="H84" s="2">
+      <c r="J84" s="2">
         <v>5</v>
       </c>
-      <c r="I84" t="s">
+      <c r="K84" t="s">
         <v>409</v>
       </c>
-      <c r="J84" s="2">
+      <c r="L84" s="2">
         <v>1</v>
       </c>
-      <c r="K84" t="s">
+      <c r="M84" t="s">
         <v>410</v>
       </c>
-      <c r="L84" s="2">
+      <c r="N84" s="2">
         <v>11</v>
       </c>
-      <c r="M84" s="12" t="s">
+      <c r="O84" s="12" t="s">
         <v>2650</v>
-      </c>
-      <c r="N84" s="8" t="s">
-        <v>2514</v>
-      </c>
-      <c r="O84" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P84" s="8" t="s">
         <v>2453</v>
@@ -20316,41 +20317,41 @@
       <c r="C85" t="s">
         <v>412</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="8" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F85" t="s">
         <v>61</v>
       </c>
-      <c r="E85" t="s">
+      <c r="G85" t="s">
         <v>150</v>
       </c>
-      <c r="F85" t="s">
+      <c r="H85" t="s">
         <v>413</v>
       </c>
-      <c r="G85" t="s">
+      <c r="I85" t="s">
         <v>414</v>
-      </c>
-      <c r="H85" s="2">
-        <v>3</v>
-      </c>
-      <c r="I85" t="s">
-        <v>415</v>
       </c>
       <c r="J85" s="2">
         <v>3</v>
       </c>
       <c r="K85" t="s">
+        <v>415</v>
+      </c>
+      <c r="L85" s="2">
+        <v>3</v>
+      </c>
+      <c r="M85" t="s">
         <v>328</v>
       </c>
-      <c r="L85" s="2">
+      <c r="N85" s="2">
         <v>2</v>
       </c>
-      <c r="M85" s="12" t="s">
+      <c r="O85" s="12" t="s">
         <v>2651</v>
-      </c>
-      <c r="N85" s="8" t="s">
-        <v>2515</v>
-      </c>
-      <c r="O85" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P85" s="8" t="s">
         <v>2453</v>
@@ -20366,41 +20367,41 @@
       <c r="C86" t="s">
         <v>417</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="8" t="s">
+        <v>2516</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F86" t="s">
         <v>61</v>
       </c>
-      <c r="E86" t="s">
+      <c r="G86" t="s">
         <v>150</v>
       </c>
-      <c r="F86" t="s">
+      <c r="H86" t="s">
         <v>418</v>
       </c>
-      <c r="G86" t="s">
+      <c r="I86" t="s">
         <v>419</v>
       </c>
-      <c r="H86" s="2">
+      <c r="J86" s="2">
         <v>3</v>
       </c>
-      <c r="I86" t="s">
+      <c r="K86" t="s">
         <v>409</v>
       </c>
-      <c r="J86" s="2">
+      <c r="L86" s="2">
         <v>1</v>
       </c>
-      <c r="K86" t="s">
+      <c r="M86" t="s">
         <v>328</v>
       </c>
-      <c r="L86" s="2">
+      <c r="N86" s="2">
         <v>2</v>
       </c>
-      <c r="M86" s="12" t="s">
+      <c r="O86" s="12" t="s">
         <v>2652</v>
-      </c>
-      <c r="N86" s="8" t="s">
-        <v>2516</v>
-      </c>
-      <c r="O86" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P86" s="8" t="s">
         <v>2453</v>
@@ -20416,41 +20417,41 @@
       <c r="C87" t="s">
         <v>422</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="8" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F87" t="s">
         <v>175</v>
       </c>
-      <c r="E87" t="s">
+      <c r="G87" t="s">
         <v>150</v>
       </c>
-      <c r="F87" t="s">
+      <c r="H87" t="s">
         <v>423</v>
       </c>
-      <c r="G87" t="s">
+      <c r="I87" t="s">
         <v>424</v>
       </c>
-      <c r="H87" s="2">
+      <c r="J87" s="2">
         <v>3</v>
       </c>
-      <c r="I87" t="s">
+      <c r="K87" t="s">
         <v>425</v>
       </c>
-      <c r="J87" s="2">
+      <c r="L87" s="2">
         <v>1</v>
       </c>
-      <c r="K87" t="s">
+      <c r="M87" t="s">
         <v>426</v>
       </c>
-      <c r="L87" s="2">
+      <c r="N87" s="2">
         <v>5</v>
       </c>
-      <c r="M87" s="12" t="s">
+      <c r="O87" s="12" t="s">
         <v>2653</v>
-      </c>
-      <c r="N87" s="8" t="s">
-        <v>2517</v>
-      </c>
-      <c r="O87" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P87" s="8" t="s">
         <v>2453</v>
@@ -20466,41 +20467,41 @@
       <c r="C88" t="s">
         <v>422</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="8" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F88" t="s">
         <v>175</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>150</v>
       </c>
-      <c r="F88" t="s">
+      <c r="H88" t="s">
         <v>428</v>
       </c>
-      <c r="G88" t="s">
+      <c r="I88" t="s">
         <v>429</v>
       </c>
-      <c r="H88" s="2">
+      <c r="J88" s="2">
         <v>3</v>
       </c>
-      <c r="I88" t="s">
+      <c r="K88" t="s">
         <v>425</v>
       </c>
-      <c r="J88" s="2">
+      <c r="L88" s="2">
         <v>1</v>
       </c>
-      <c r="K88" t="s">
+      <c r="M88" t="s">
         <v>430</v>
       </c>
-      <c r="L88" s="2">
+      <c r="N88" s="2">
         <v>5</v>
       </c>
-      <c r="M88" s="12" t="s">
+      <c r="O88" s="12" t="s">
         <v>2654</v>
-      </c>
-      <c r="N88" s="8" t="s">
-        <v>2517</v>
-      </c>
-      <c r="O88" s="8" t="s">
-        <v>2507</v>
       </c>
       <c r="P88" s="8" t="s">
         <v>2453</v>
@@ -20516,41 +20517,41 @@
       <c r="C89" t="s">
         <v>433</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="8" t="s">
+        <v>2518</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F89" t="s">
         <v>434</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>183</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" t="s">
         <v>435</v>
       </c>
-      <c r="G89" t="s">
+      <c r="I89" t="s">
         <v>436</v>
       </c>
-      <c r="H89" s="2">
+      <c r="J89" s="2">
         <v>4</v>
       </c>
-      <c r="I89" t="s">
+      <c r="K89" t="s">
         <v>437</v>
-      </c>
-      <c r="J89" s="2">
-        <v>5</v>
-      </c>
-      <c r="K89" t="s">
-        <v>75</v>
       </c>
       <c r="L89" s="2">
         <v>5</v>
       </c>
-      <c r="M89" s="12" t="s">
+      <c r="M89" t="s">
+        <v>75</v>
+      </c>
+      <c r="N89" s="2">
+        <v>5</v>
+      </c>
+      <c r="O89" s="12" t="s">
         <v>2655</v>
-      </c>
-      <c r="N89" s="8" t="s">
-        <v>2518</v>
-      </c>
-      <c r="O89" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P89" s="8" t="s">
         <v>2411</v>
@@ -20566,41 +20567,41 @@
       <c r="C90" t="s">
         <v>439</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="8" t="s">
+        <v>2519</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F90" t="s">
         <v>434</v>
       </c>
-      <c r="E90" t="s">
+      <c r="G90" t="s">
         <v>285</v>
       </c>
-      <c r="F90" t="s">
+      <c r="H90" t="s">
         <v>440</v>
       </c>
-      <c r="G90" t="s">
+      <c r="I90" t="s">
         <v>441</v>
       </c>
-      <c r="H90" s="2">
+      <c r="J90" s="2">
         <v>2</v>
       </c>
-      <c r="I90" t="s">
+      <c r="K90" t="s">
         <v>442</v>
-      </c>
-      <c r="J90" s="2">
-        <v>5</v>
-      </c>
-      <c r="K90" t="s">
-        <v>75</v>
       </c>
       <c r="L90" s="2">
         <v>5</v>
       </c>
-      <c r="M90" s="12" t="s">
+      <c r="M90" t="s">
+        <v>75</v>
+      </c>
+      <c r="N90" s="2">
+        <v>5</v>
+      </c>
+      <c r="O90" s="12" t="s">
         <v>2656</v>
-      </c>
-      <c r="N90" s="8" t="s">
-        <v>2519</v>
-      </c>
-      <c r="O90" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P90" s="8" t="s">
         <v>2411</v>
@@ -20616,41 +20617,41 @@
       <c r="C91" t="s">
         <v>445</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="8" t="s">
+        <v>2520</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F91" t="s">
         <v>434</v>
       </c>
-      <c r="E91" t="s">
+      <c r="G91" t="s">
         <v>71</v>
       </c>
-      <c r="F91" t="s">
+      <c r="H91" t="s">
         <v>446</v>
       </c>
-      <c r="G91" t="s">
+      <c r="I91" t="s">
         <v>447</v>
       </c>
-      <c r="H91" s="2">
+      <c r="J91" s="2">
         <v>3</v>
       </c>
-      <c r="I91" t="s">
+      <c r="K91" t="s">
         <v>448</v>
-      </c>
-      <c r="J91" s="2">
-        <v>5</v>
-      </c>
-      <c r="K91" t="s">
-        <v>75</v>
       </c>
       <c r="L91" s="2">
         <v>5</v>
       </c>
-      <c r="M91" s="12" t="s">
+      <c r="M91" t="s">
+        <v>75</v>
+      </c>
+      <c r="N91" s="2">
+        <v>5</v>
+      </c>
+      <c r="O91" s="12" t="s">
         <v>2657</v>
-      </c>
-      <c r="N91" s="8" t="s">
-        <v>2520</v>
-      </c>
-      <c r="O91" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P91" s="8" t="s">
         <v>2411</v>
@@ -20666,26 +20667,26 @@
       <c r="C92" t="s">
         <v>450</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="8" t="s">
+        <v>2521</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F92" t="s">
         <v>434</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>150</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H92" t="s">
         <v>451</v>
       </c>
-      <c r="G92" t="s">
+      <c r="I92" t="s">
         <v>452</v>
       </c>
-      <c r="H92" s="2">
+      <c r="J92" s="2">
         <v>2</v>
-      </c>
-      <c r="I92" t="s">
-        <v>48</v>
-      </c>
-      <c r="J92" s="2">
-        <v>0</v>
       </c>
       <c r="K92" t="s">
         <v>48</v>
@@ -20693,14 +20694,14 @@
       <c r="L92" s="2">
         <v>0</v>
       </c>
-      <c r="M92" s="12" t="s">
+      <c r="M92" t="s">
+        <v>48</v>
+      </c>
+      <c r="N92" s="2">
+        <v>0</v>
+      </c>
+      <c r="O92" s="12" t="s">
         <v>2658</v>
-      </c>
-      <c r="N92" s="8" t="s">
-        <v>2521</v>
-      </c>
-      <c r="O92" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P92" s="8" t="s">
         <v>2412</v>
@@ -20716,26 +20717,26 @@
       <c r="C93" t="s">
         <v>454</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="8" t="s">
+        <v>2522</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F93" t="s">
         <v>434</v>
       </c>
-      <c r="E93" t="s">
+      <c r="G93" t="s">
         <v>96</v>
       </c>
-      <c r="F93" t="s">
+      <c r="H93" t="s">
         <v>455</v>
       </c>
-      <c r="G93" t="s">
+      <c r="I93" t="s">
         <v>456</v>
       </c>
-      <c r="H93" s="2">
+      <c r="J93" s="2">
         <v>2</v>
-      </c>
-      <c r="I93" t="s">
-        <v>48</v>
-      </c>
-      <c r="J93" s="2">
-        <v>0</v>
       </c>
       <c r="K93" t="s">
         <v>48</v>
@@ -20743,14 +20744,14 @@
       <c r="L93" s="2">
         <v>0</v>
       </c>
-      <c r="M93" s="12" t="s">
+      <c r="M93" t="s">
+        <v>48</v>
+      </c>
+      <c r="N93" s="2">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="s">
         <v>2659</v>
-      </c>
-      <c r="N93" s="8" t="s">
-        <v>2522</v>
-      </c>
-      <c r="O93" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P93" s="8" t="s">
         <v>2412</v>
@@ -20766,41 +20767,41 @@
       <c r="C94" t="s">
         <v>458</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="8" t="s">
+        <v>2523</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F94" t="s">
         <v>434</v>
       </c>
-      <c r="E94" t="s">
+      <c r="G94" t="s">
         <v>150</v>
       </c>
-      <c r="F94" t="s">
+      <c r="H94" t="s">
         <v>459</v>
       </c>
-      <c r="G94" t="s">
+      <c r="I94" t="s">
         <v>460</v>
-      </c>
-      <c r="H94" s="2">
-        <v>5</v>
-      </c>
-      <c r="I94" t="s">
-        <v>461</v>
       </c>
       <c r="J94" s="2">
         <v>5</v>
       </c>
       <c r="K94" t="s">
+        <v>461</v>
+      </c>
+      <c r="L94" s="2">
+        <v>5</v>
+      </c>
+      <c r="M94" t="s">
         <v>462</v>
       </c>
-      <c r="L94" s="2">
+      <c r="N94" s="2">
         <v>1</v>
       </c>
-      <c r="M94" s="12" t="s">
+      <c r="O94" s="12" t="s">
         <v>2660</v>
-      </c>
-      <c r="N94" s="8" t="s">
-        <v>2523</v>
-      </c>
-      <c r="O94" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P94" s="8" t="s">
         <v>2412</v>
@@ -20816,41 +20817,41 @@
       <c r="C95" t="s">
         <v>464</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="8" t="s">
+        <v>2524</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F95" t="s">
         <v>434</v>
       </c>
-      <c r="E95" t="s">
+      <c r="G95" t="s">
         <v>465</v>
       </c>
-      <c r="F95" t="s">
+      <c r="H95" t="s">
         <v>466</v>
       </c>
-      <c r="G95" t="s">
+      <c r="I95" t="s">
         <v>467</v>
       </c>
-      <c r="H95" s="2">
+      <c r="J95" s="2">
         <v>3</v>
       </c>
-      <c r="I95" t="s">
+      <c r="K95" t="s">
         <v>468</v>
-      </c>
-      <c r="J95" s="2">
-        <v>5</v>
-      </c>
-      <c r="K95" t="s">
-        <v>75</v>
       </c>
       <c r="L95" s="2">
         <v>5</v>
       </c>
-      <c r="M95" s="12" t="s">
+      <c r="M95" t="s">
+        <v>75</v>
+      </c>
+      <c r="N95" s="2">
+        <v>5</v>
+      </c>
+      <c r="O95" s="12" t="s">
         <v>2661</v>
-      </c>
-      <c r="N95" s="8" t="s">
-        <v>2524</v>
-      </c>
-      <c r="O95" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P95" s="8" t="s">
         <v>2412</v>
@@ -20866,41 +20867,41 @@
       <c r="C96" t="s">
         <v>471</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="8" t="s">
+        <v>2525</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F96" t="s">
         <v>434</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>150</v>
       </c>
-      <c r="F96" t="s">
+      <c r="H96" t="s">
         <v>472</v>
       </c>
-      <c r="G96" t="s">
+      <c r="I96" t="s">
         <v>473</v>
       </c>
-      <c r="H96" s="2">
+      <c r="J96" s="2">
         <v>2</v>
       </c>
-      <c r="I96" t="s">
+      <c r="K96" t="s">
         <v>474</v>
       </c>
-      <c r="J96" s="2">
+      <c r="L96" s="2">
         <v>5</v>
       </c>
-      <c r="K96" t="s">
+      <c r="M96" t="s">
         <v>475</v>
       </c>
-      <c r="L96" s="2">
+      <c r="N96" s="2">
         <v>1</v>
       </c>
-      <c r="M96" s="12" t="s">
+      <c r="O96" s="12" t="s">
         <v>2662</v>
-      </c>
-      <c r="N96" s="8" t="s">
-        <v>2525</v>
-      </c>
-      <c r="O96" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P96" s="8" t="s">
         <v>2411</v>
@@ -20916,41 +20917,41 @@
       <c r="C97" t="s">
         <v>477</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="8" t="s">
+        <v>2526</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F97" t="s">
         <v>434</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>118</v>
       </c>
-      <c r="F97" t="s">
+      <c r="H97" t="s">
         <v>478</v>
       </c>
-      <c r="G97" t="s">
+      <c r="I97" t="s">
         <v>479</v>
-      </c>
-      <c r="H97" s="2">
-        <v>4</v>
-      </c>
-      <c r="I97" t="s">
-        <v>480</v>
       </c>
       <c r="J97" s="2">
         <v>4</v>
       </c>
       <c r="K97" t="s">
+        <v>480</v>
+      </c>
+      <c r="L97" s="2">
+        <v>4</v>
+      </c>
+      <c r="M97" t="s">
         <v>48</v>
       </c>
-      <c r="L97" s="2">
+      <c r="N97" s="2">
         <v>0</v>
       </c>
-      <c r="M97" s="12" t="s">
+      <c r="O97" s="12" t="s">
         <v>2663</v>
-      </c>
-      <c r="N97" s="8" t="s">
-        <v>2526</v>
-      </c>
-      <c r="O97" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P97" s="8" t="s">
         <v>2411</v>
@@ -20966,41 +20967,41 @@
       <c r="C98" t="s">
         <v>482</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="8" t="s">
+        <v>2527</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F98" t="s">
         <v>434</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>483</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" t="s">
         <v>484</v>
       </c>
-      <c r="G98" t="s">
+      <c r="I98" t="s">
         <v>485</v>
       </c>
-      <c r="H98" s="2">
+      <c r="J98" s="2">
         <v>2</v>
       </c>
-      <c r="I98" t="s">
+      <c r="K98" t="s">
         <v>48</v>
       </c>
-      <c r="J98" s="2">
+      <c r="L98" s="2">
         <v>0</v>
       </c>
-      <c r="K98" t="s">
+      <c r="M98" t="s">
         <v>75</v>
       </c>
-      <c r="L98" s="2">
+      <c r="N98" s="2">
         <v>5</v>
       </c>
-      <c r="M98" s="12" t="s">
+      <c r="O98" s="12" t="s">
         <v>2664</v>
-      </c>
-      <c r="N98" s="8" t="s">
-        <v>2527</v>
-      </c>
-      <c r="O98" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P98" s="8" t="s">
         <v>2413</v>
@@ -21016,41 +21017,41 @@
       <c r="C99" t="s">
         <v>487</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="8" t="s">
+        <v>2528</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F99" t="s">
         <v>434</v>
       </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>107</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" t="s">
         <v>484</v>
       </c>
-      <c r="G99" t="s">
+      <c r="I99" t="s">
         <v>485</v>
       </c>
-      <c r="H99" s="2">
+      <c r="J99" s="2">
         <v>2</v>
       </c>
-      <c r="I99" t="s">
+      <c r="K99" t="s">
         <v>48</v>
       </c>
-      <c r="J99" s="2">
+      <c r="L99" s="2">
         <v>0</v>
       </c>
-      <c r="K99" t="s">
+      <c r="M99" t="s">
         <v>75</v>
       </c>
-      <c r="L99" s="2">
+      <c r="N99" s="2">
         <v>5</v>
       </c>
-      <c r="M99" s="12" t="s">
+      <c r="O99" s="12" t="s">
         <v>2665</v>
-      </c>
-      <c r="N99" s="8" t="s">
-        <v>2528</v>
-      </c>
-      <c r="O99" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P99" s="8" t="s">
         <v>2414</v>
@@ -21066,41 +21067,41 @@
       <c r="C100" t="s">
         <v>489</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="8" t="s">
+        <v>2529</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F100" t="s">
         <v>434</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>112</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
         <v>490</v>
       </c>
-      <c r="G100" t="s">
+      <c r="I100" t="s">
         <v>491</v>
       </c>
-      <c r="H100" s="2">
+      <c r="J100" s="2">
         <v>2</v>
       </c>
-      <c r="I100" t="s">
+      <c r="K100" t="s">
         <v>48</v>
       </c>
-      <c r="J100" s="2">
+      <c r="L100" s="2">
         <v>0</v>
       </c>
-      <c r="K100" t="s">
+      <c r="M100" t="s">
         <v>75</v>
       </c>
-      <c r="L100" s="2">
+      <c r="N100" s="2">
         <v>5</v>
       </c>
-      <c r="M100" s="12" t="s">
+      <c r="O100" s="12" t="s">
         <v>2666</v>
-      </c>
-      <c r="N100" s="8" t="s">
-        <v>2529</v>
-      </c>
-      <c r="O100" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P100" s="8" t="s">
         <v>2530</v>
@@ -21116,41 +21117,41 @@
       <c r="C101" t="s">
         <v>494</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="8" t="s">
+        <v>2531</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F101" t="s">
         <v>434</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>285</v>
       </c>
-      <c r="F101" t="s">
+      <c r="H101" t="s">
         <v>495</v>
       </c>
-      <c r="G101" t="s">
+      <c r="I101" t="s">
         <v>496</v>
       </c>
-      <c r="H101" s="2">
+      <c r="J101" s="2">
         <v>2</v>
       </c>
-      <c r="I101" t="s">
+      <c r="K101" t="s">
         <v>48</v>
       </c>
-      <c r="J101" s="2">
+      <c r="L101" s="2">
         <v>0</v>
       </c>
-      <c r="K101" t="s">
+      <c r="M101" t="s">
         <v>75</v>
       </c>
-      <c r="L101" s="2">
+      <c r="N101" s="2">
         <v>5</v>
       </c>
-      <c r="M101" s="12" t="s">
+      <c r="O101" s="12" t="s">
         <v>2667</v>
-      </c>
-      <c r="N101" s="8" t="s">
-        <v>2531</v>
-      </c>
-      <c r="O101" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P101" s="8" t="s">
         <v>2412</v>
@@ -21166,41 +21167,41 @@
       <c r="C102" t="s">
         <v>499</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="8" t="s">
+        <v>2532</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F102" t="s">
         <v>434</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>150</v>
       </c>
-      <c r="F102" t="s">
+      <c r="H102" t="s">
         <v>500</v>
       </c>
-      <c r="G102" t="s">
+      <c r="I102" t="s">
         <v>501</v>
       </c>
-      <c r="H102" s="2">
+      <c r="J102" s="2">
         <v>1</v>
       </c>
-      <c r="I102" t="s">
+      <c r="K102" t="s">
         <v>502</v>
       </c>
-      <c r="J102" s="2">
+      <c r="L102" s="2">
         <v>2</v>
       </c>
-      <c r="K102" t="s">
+      <c r="M102" t="s">
         <v>48</v>
       </c>
-      <c r="L102" s="2">
+      <c r="N102" s="2">
         <v>0</v>
       </c>
-      <c r="M102" s="12" t="s">
+      <c r="O102" s="12" t="s">
         <v>2668</v>
-      </c>
-      <c r="N102" s="8" t="s">
-        <v>2532</v>
-      </c>
-      <c r="O102" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P102" s="8" t="s">
         <v>2411</v>
@@ -21216,41 +21217,41 @@
       <c r="C103" t="s">
         <v>504</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="8" t="s">
+        <v>2533</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F103" t="s">
         <v>434</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>150</v>
       </c>
-      <c r="F103" t="s">
+      <c r="H103" t="s">
         <v>505</v>
       </c>
-      <c r="G103" t="s">
+      <c r="I103" t="s">
         <v>506</v>
       </c>
-      <c r="H103" s="2">
+      <c r="J103" s="2">
         <v>1</v>
       </c>
-      <c r="I103" t="s">
+      <c r="K103" t="s">
         <v>507</v>
       </c>
-      <c r="J103" s="2">
+      <c r="L103" s="2">
         <v>5</v>
       </c>
-      <c r="K103" t="s">
+      <c r="M103" t="s">
         <v>48</v>
       </c>
-      <c r="L103" s="2">
+      <c r="N103" s="2">
         <v>0</v>
       </c>
-      <c r="M103" s="12" t="s">
+      <c r="O103" s="12" t="s">
         <v>2669</v>
-      </c>
-      <c r="N103" s="8" t="s">
-        <v>2533</v>
-      </c>
-      <c r="O103" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P103" s="8" t="s">
         <v>2411</v>
@@ -21266,41 +21267,41 @@
       <c r="C104" t="s">
         <v>509</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="8" t="s">
+        <v>2534</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F104" t="s">
         <v>434</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>150</v>
       </c>
-      <c r="F104" t="s">
+      <c r="H104" t="s">
         <v>510</v>
       </c>
-      <c r="G104" t="s">
+      <c r="I104" t="s">
         <v>511</v>
       </c>
-      <c r="H104" s="2">
+      <c r="J104" s="2">
         <v>1</v>
       </c>
-      <c r="I104" t="s">
+      <c r="K104" t="s">
         <v>512</v>
       </c>
-      <c r="J104" s="2">
+      <c r="L104" s="2">
         <v>4</v>
       </c>
-      <c r="K104" t="s">
+      <c r="M104" t="s">
         <v>48</v>
       </c>
-      <c r="L104" s="2">
+      <c r="N104" s="2">
         <v>0</v>
       </c>
-      <c r="M104" s="12" t="s">
+      <c r="O104" s="12" t="s">
         <v>2670</v>
-      </c>
-      <c r="N104" s="8" t="s">
-        <v>2534</v>
-      </c>
-      <c r="O104" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P104" s="8" t="s">
         <v>2411</v>
@@ -21316,41 +21317,41 @@
       <c r="C105" t="s">
         <v>514</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="8" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F105" t="s">
         <v>434</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>150</v>
       </c>
-      <c r="F105" t="s">
+      <c r="H105" t="s">
         <v>515</v>
       </c>
-      <c r="G105" t="s">
+      <c r="I105" t="s">
         <v>516</v>
       </c>
-      <c r="H105" s="2">
+      <c r="J105" s="2">
         <v>1</v>
       </c>
-      <c r="I105" t="s">
+      <c r="K105" t="s">
         <v>517</v>
       </c>
-      <c r="J105" s="2">
+      <c r="L105" s="2">
         <v>2</v>
       </c>
-      <c r="K105" t="s">
+      <c r="M105" t="s">
         <v>48</v>
       </c>
-      <c r="L105" s="2">
+      <c r="N105" s="2">
         <v>0</v>
       </c>
-      <c r="M105" s="12" t="s">
+      <c r="O105" s="12" t="s">
         <v>2671</v>
-      </c>
-      <c r="N105" s="8" t="s">
-        <v>2535</v>
-      </c>
-      <c r="O105" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P105" s="8" t="s">
         <v>2411</v>
@@ -21366,41 +21367,41 @@
       <c r="C106" t="s">
         <v>477</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="8" t="s">
+        <v>2526</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F106" t="s">
         <v>434</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>118</v>
       </c>
-      <c r="F106" t="s">
+      <c r="H106" t="s">
         <v>478</v>
       </c>
-      <c r="G106" t="s">
+      <c r="I106" t="s">
         <v>479</v>
-      </c>
-      <c r="H106" s="2">
-        <v>4</v>
-      </c>
-      <c r="I106" t="s">
-        <v>480</v>
       </c>
       <c r="J106" s="2">
         <v>4</v>
       </c>
       <c r="K106" t="s">
+        <v>480</v>
+      </c>
+      <c r="L106" s="2">
+        <v>4</v>
+      </c>
+      <c r="M106" t="s">
         <v>48</v>
       </c>
-      <c r="L106" s="2">
+      <c r="N106" s="2">
         <v>0</v>
       </c>
-      <c r="M106" s="12" t="s">
+      <c r="O106" s="12" t="s">
         <v>2672</v>
-      </c>
-      <c r="N106" s="8" t="s">
-        <v>2526</v>
-      </c>
-      <c r="O106" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P106" s="8" t="s">
         <v>2411</v>
@@ -21416,26 +21417,24 @@
       <c r="C107" t="s">
         <v>521</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="8" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E107" s="8"/>
+      <c r="F107" t="s">
         <v>434</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>118</v>
       </c>
-      <c r="F107" t="s">
+      <c r="H107" t="s">
         <v>522</v>
       </c>
-      <c r="G107" t="s">
+      <c r="I107" t="s">
         <v>523</v>
       </c>
-      <c r="H107" s="2">
+      <c r="J107" s="2">
         <v>1</v>
-      </c>
-      <c r="I107" t="s">
-        <v>48</v>
-      </c>
-      <c r="J107" s="2">
-        <v>0</v>
       </c>
       <c r="K107" t="s">
         <v>48</v>
@@ -21443,13 +21442,15 @@
       <c r="L107" s="2">
         <v>0</v>
       </c>
-      <c r="M107" s="12" t="s">
+      <c r="M107" t="s">
+        <v>48</v>
+      </c>
+      <c r="N107" s="2">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="s">
         <v>2673</v>
       </c>
-      <c r="N107" s="8" t="s">
-        <v>2536</v>
-      </c>
-      <c r="O107" s="8"/>
       <c r="P107" s="8" t="s">
         <v>2419</v>
       </c>
@@ -21464,26 +21465,24 @@
       <c r="C108" t="s">
         <v>525</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="8" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E108" s="8"/>
+      <c r="F108" t="s">
         <v>434</v>
       </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>118</v>
       </c>
-      <c r="F108" t="s">
+      <c r="H108" t="s">
         <v>526</v>
       </c>
-      <c r="G108" t="s">
+      <c r="I108" t="s">
         <v>527</v>
       </c>
-      <c r="H108" s="2">
+      <c r="J108" s="2">
         <v>2</v>
-      </c>
-      <c r="I108" t="s">
-        <v>48</v>
-      </c>
-      <c r="J108" s="2">
-        <v>0</v>
       </c>
       <c r="K108" t="s">
         <v>48</v>
@@ -21491,13 +21490,15 @@
       <c r="L108" s="2">
         <v>0</v>
       </c>
-      <c r="M108" s="12" t="s">
+      <c r="M108" t="s">
+        <v>48</v>
+      </c>
+      <c r="N108" s="2">
+        <v>0</v>
+      </c>
+      <c r="O108" s="12" t="s">
         <v>2674</v>
       </c>
-      <c r="N108" s="8" t="s">
-        <v>2536</v>
-      </c>
-      <c r="O108" s="8"/>
       <c r="P108" s="8" t="s">
         <v>2419</v>
       </c>
@@ -21512,26 +21513,24 @@
       <c r="C109" t="s">
         <v>529</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="8" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E109" s="8"/>
+      <c r="F109" t="s">
         <v>434</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>118</v>
       </c>
-      <c r="F109" t="s">
+      <c r="H109" t="s">
         <v>530</v>
       </c>
-      <c r="G109" t="s">
+      <c r="I109" t="s">
         <v>531</v>
       </c>
-      <c r="H109" s="2">
+      <c r="J109" s="2">
         <v>3</v>
-      </c>
-      <c r="I109" t="s">
-        <v>48</v>
-      </c>
-      <c r="J109" s="2">
-        <v>0</v>
       </c>
       <c r="K109" t="s">
         <v>48</v>
@@ -21539,13 +21538,15 @@
       <c r="L109" s="2">
         <v>0</v>
       </c>
-      <c r="M109" s="12" t="s">
+      <c r="M109" t="s">
+        <v>48</v>
+      </c>
+      <c r="N109" s="2">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="s">
         <v>2675</v>
       </c>
-      <c r="N109" s="8" t="s">
-        <v>2536</v>
-      </c>
-      <c r="O109" s="8"/>
       <c r="P109" s="8" t="s">
         <v>2419</v>
       </c>
@@ -21560,26 +21561,24 @@
       <c r="C110" t="s">
         <v>533</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="8" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E110" s="8"/>
+      <c r="F110" t="s">
         <v>434</v>
       </c>
-      <c r="E110" t="s">
+      <c r="G110" t="s">
         <v>118</v>
       </c>
-      <c r="F110" t="s">
+      <c r="H110" t="s">
         <v>534</v>
       </c>
-      <c r="G110" t="s">
+      <c r="I110" t="s">
         <v>535</v>
       </c>
-      <c r="H110" s="2">
+      <c r="J110" s="2">
         <v>1</v>
-      </c>
-      <c r="I110" t="s">
-        <v>48</v>
-      </c>
-      <c r="J110" s="2">
-        <v>0</v>
       </c>
       <c r="K110" t="s">
         <v>48</v>
@@ -21587,13 +21586,15 @@
       <c r="L110" s="2">
         <v>0</v>
       </c>
-      <c r="M110" s="12" t="s">
+      <c r="M110" t="s">
+        <v>48</v>
+      </c>
+      <c r="N110" s="2">
+        <v>0</v>
+      </c>
+      <c r="O110" s="12" t="s">
         <v>2676</v>
       </c>
-      <c r="N110" s="8" t="s">
-        <v>2536</v>
-      </c>
-      <c r="O110" s="8"/>
       <c r="P110" s="8" t="s">
         <v>2419</v>
       </c>
@@ -21608,41 +21609,41 @@
       <c r="C111" t="s">
         <v>537</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="8" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F111" t="s">
         <v>434</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>118</v>
       </c>
-      <c r="F111" t="s">
+      <c r="H111" t="s">
         <v>500</v>
       </c>
-      <c r="G111" t="s">
+      <c r="I111" t="s">
         <v>501</v>
       </c>
-      <c r="H111" s="2">
+      <c r="J111" s="2">
         <v>1</v>
       </c>
-      <c r="I111" t="s">
+      <c r="K111" t="s">
         <v>502</v>
       </c>
-      <c r="J111" s="2">
+      <c r="L111" s="2">
         <v>2</v>
       </c>
-      <c r="K111" t="s">
+      <c r="M111" t="s">
         <v>48</v>
       </c>
-      <c r="L111" s="2">
+      <c r="N111" s="2">
         <v>0</v>
       </c>
-      <c r="M111" s="12" t="s">
+      <c r="O111" s="12" t="s">
         <v>2677</v>
-      </c>
-      <c r="N111" s="8" t="s">
-        <v>2537</v>
-      </c>
-      <c r="O111" s="8" t="s">
-        <v>2538</v>
       </c>
       <c r="P111" s="8" t="s">
         <v>2419</v>
@@ -21658,41 +21659,41 @@
       <c r="C112" t="s">
         <v>540</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="8" t="s">
+        <v>2539</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F112" t="s">
         <v>434</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>80</v>
       </c>
-      <c r="F112" t="s">
+      <c r="H112" t="s">
         <v>541</v>
       </c>
-      <c r="G112" t="s">
+      <c r="I112" t="s">
         <v>542</v>
       </c>
-      <c r="H112" s="2">
+      <c r="J112" s="2">
         <v>5</v>
       </c>
-      <c r="I112" t="s">
+      <c r="K112" t="s">
         <v>48</v>
       </c>
-      <c r="J112" s="2">
+      <c r="L112" s="2">
         <v>0</v>
       </c>
-      <c r="K112" t="s">
+      <c r="M112" t="s">
         <v>153</v>
       </c>
-      <c r="L112" s="2">
+      <c r="N112" s="2">
         <v>7</v>
       </c>
-      <c r="M112" s="12" t="s">
+      <c r="O112" s="12" t="s">
         <v>2678</v>
-      </c>
-      <c r="N112" s="8" t="s">
-        <v>2539</v>
-      </c>
-      <c r="O112" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P112" s="8" t="s">
         <v>2411</v>
@@ -21708,41 +21709,41 @@
       <c r="C113" t="s">
         <v>544</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="8" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F113" t="s">
         <v>434</v>
       </c>
-      <c r="E113" t="s">
+      <c r="G113" t="s">
         <v>115</v>
       </c>
-      <c r="F113" t="s">
+      <c r="H113" t="s">
         <v>545</v>
       </c>
-      <c r="G113" t="s">
+      <c r="I113" t="s">
         <v>546</v>
       </c>
-      <c r="H113" s="2">
+      <c r="J113" s="2">
         <v>2</v>
       </c>
-      <c r="I113" t="s">
+      <c r="K113" t="s">
         <v>48</v>
       </c>
-      <c r="J113" s="2">
+      <c r="L113" s="2">
         <v>0</v>
       </c>
-      <c r="K113" t="s">
+      <c r="M113" t="s">
         <v>153</v>
       </c>
-      <c r="L113" s="2">
+      <c r="N113" s="2">
         <v>7</v>
       </c>
-      <c r="M113" s="12" t="s">
+      <c r="O113" s="12" t="s">
         <v>2679</v>
-      </c>
-      <c r="N113" s="8" t="s">
-        <v>2540</v>
-      </c>
-      <c r="O113" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P113" s="8" t="s">
         <v>2411</v>
@@ -21758,41 +21759,41 @@
       <c r="C114" t="s">
         <v>548</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="8" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F114" t="s">
         <v>434</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>96</v>
       </c>
-      <c r="F114" t="s">
+      <c r="H114" t="s">
         <v>549</v>
       </c>
-      <c r="G114" t="s">
+      <c r="I114" t="s">
         <v>550</v>
       </c>
-      <c r="H114" s="2">
+      <c r="J114" s="2">
         <v>4</v>
       </c>
-      <c r="I114" t="s">
+      <c r="K114" t="s">
         <v>48</v>
       </c>
-      <c r="J114" s="2">
+      <c r="L114" s="2">
         <v>0</v>
       </c>
-      <c r="K114" t="s">
+      <c r="M114" t="s">
         <v>75</v>
       </c>
-      <c r="L114" s="2">
+      <c r="N114" s="2">
         <v>5</v>
       </c>
-      <c r="M114" s="12" t="s">
+      <c r="O114" s="12" t="s">
         <v>2680</v>
-      </c>
-      <c r="N114" s="8" t="s">
-        <v>2541</v>
-      </c>
-      <c r="O114" s="8" t="s">
-        <v>2406</v>
       </c>
       <c r="P114" s="8" t="s">
         <v>2411</v>
@@ -21808,41 +21809,41 @@
       <c r="C115" t="s">
         <v>553</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="8" t="s">
+        <v>2542</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F115" t="s">
         <v>61</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>150</v>
       </c>
-      <c r="F115" t="s">
+      <c r="H115" t="s">
         <v>554</v>
       </c>
-      <c r="G115" t="s">
+      <c r="I115" t="s">
         <v>555</v>
       </c>
-      <c r="H115" s="2">
+      <c r="J115" s="2">
         <v>3</v>
       </c>
-      <c r="I115" t="s">
+      <c r="K115" t="s">
         <v>556</v>
       </c>
-      <c r="J115" s="2">
+      <c r="L115" s="2">
         <v>1</v>
       </c>
-      <c r="K115" t="s">
+      <c r="M115" t="s">
         <v>328</v>
       </c>
-      <c r="L115" s="2">
+      <c r="N115" s="2">
         <v>2</v>
       </c>
-      <c r="M115" s="12" t="s">
+      <c r="O115" s="12" t="s">
         <v>2681</v>
-      </c>
-      <c r="N115" s="8" t="s">
-        <v>2542</v>
-      </c>
-      <c r="O115" s="8" t="s">
-        <v>2543</v>
       </c>
       <c r="P115" s="8" t="s">
         <v>2453</v>
@@ -21858,41 +21859,41 @@
       <c r="C116" t="s">
         <v>558</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="8" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F116" t="s">
         <v>61</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>71</v>
       </c>
-      <c r="F116" t="s">
+      <c r="H116" t="s">
         <v>559</v>
       </c>
-      <c r="G116" t="s">
+      <c r="I116" t="s">
         <v>560</v>
       </c>
-      <c r="H116" s="2">
+      <c r="J116" s="2">
         <v>4</v>
       </c>
-      <c r="I116" t="s">
+      <c r="K116" t="s">
         <v>561</v>
       </c>
-      <c r="J116" s="2">
+      <c r="L116" s="2">
         <v>2</v>
       </c>
-      <c r="K116" t="s">
+      <c r="M116" t="s">
         <v>562</v>
       </c>
-      <c r="L116" s="2">
+      <c r="N116" s="2">
         <v>11</v>
       </c>
-      <c r="M116" s="12" t="s">
+      <c r="O116" s="12" t="s">
         <v>2682</v>
-      </c>
-      <c r="N116" s="8" t="s">
-        <v>2544</v>
-      </c>
-      <c r="O116" s="8" t="s">
-        <v>2543</v>
       </c>
       <c r="P116" s="8" t="s">
         <v>2453</v>
@@ -21908,41 +21909,41 @@
       <c r="C117" t="s">
         <v>564</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="8" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F117" t="s">
         <v>61</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>71</v>
       </c>
-      <c r="F117" t="s">
+      <c r="H117" t="s">
         <v>565</v>
       </c>
-      <c r="G117" t="s">
+      <c r="I117" t="s">
         <v>566</v>
       </c>
-      <c r="H117" s="2">
+      <c r="J117" s="2">
         <v>6</v>
       </c>
-      <c r="I117" t="s">
+      <c r="K117" t="s">
         <v>567</v>
       </c>
-      <c r="J117" s="2">
+      <c r="L117" s="2">
         <v>5</v>
       </c>
-      <c r="K117" t="s">
+      <c r="M117" t="s">
         <v>328</v>
       </c>
-      <c r="L117" s="2">
+      <c r="N117" s="2">
         <v>2</v>
       </c>
-      <c r="M117" s="12" t="s">
+      <c r="O117" s="12" t="s">
         <v>2683</v>
-      </c>
-      <c r="N117" s="8" t="s">
-        <v>2545</v>
-      </c>
-      <c r="O117" s="8" t="s">
-        <v>2543</v>
       </c>
       <c r="P117" s="8" t="s">
         <v>2453</v>
@@ -21958,41 +21959,41 @@
       <c r="C118" t="s">
         <v>569</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="8" t="s">
+        <v>2546</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F118" t="s">
         <v>61</v>
       </c>
-      <c r="E118" t="s">
+      <c r="G118" t="s">
         <v>71</v>
       </c>
-      <c r="F118" t="s">
+      <c r="H118" t="s">
         <v>570</v>
       </c>
-      <c r="G118" t="s">
+      <c r="I118" t="s">
         <v>571</v>
       </c>
-      <c r="H118" s="2">
+      <c r="J118" s="2">
         <v>7</v>
       </c>
-      <c r="I118" t="s">
+      <c r="K118" t="s">
         <v>572</v>
       </c>
-      <c r="J118" s="2">
+      <c r="L118" s="2">
         <v>5</v>
       </c>
-      <c r="K118" t="s">
+      <c r="M118" t="s">
         <v>328</v>
       </c>
-      <c r="L118" s="2">
+      <c r="N118" s="2">
         <v>2</v>
       </c>
-      <c r="M118" s="12" t="s">
+      <c r="O118" s="12" t="s">
         <v>2684</v>
-      </c>
-      <c r="N118" s="8" t="s">
-        <v>2546</v>
-      </c>
-      <c r="O118" s="8" t="s">
-        <v>2543</v>
       </c>
       <c r="P118" s="8" t="s">
         <v>2453</v>
@@ -22008,41 +22009,41 @@
       <c r="C119" t="s">
         <v>574</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="8" t="s">
+        <v>2547</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F119" t="s">
         <v>61</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>71</v>
       </c>
-      <c r="F119" t="s">
+      <c r="H119" t="s">
         <v>575</v>
       </c>
-      <c r="G119" t="s">
+      <c r="I119" t="s">
         <v>576</v>
       </c>
-      <c r="H119" s="2">
+      <c r="J119" s="2">
         <v>7</v>
       </c>
-      <c r="I119" t="s">
+      <c r="K119" t="s">
         <v>577</v>
       </c>
-      <c r="J119" s="2">
+      <c r="L119" s="2">
         <v>3</v>
       </c>
-      <c r="K119" t="s">
+      <c r="M119" t="s">
         <v>328</v>
       </c>
-      <c r="L119" s="2">
+      <c r="N119" s="2">
         <v>2</v>
       </c>
-      <c r="M119" s="12" t="s">
+      <c r="O119" s="12" t="s">
         <v>2685</v>
-      </c>
-      <c r="N119" s="8" t="s">
-        <v>2547</v>
-      </c>
-      <c r="O119" s="8" t="s">
-        <v>2543</v>
       </c>
       <c r="P119" s="8" t="s">
         <v>2453</v>
@@ -22058,41 +22059,41 @@
       <c r="C120" t="s">
         <v>579</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="8" t="s">
+        <v>2548</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>2549</v>
+      </c>
+      <c r="F120" t="s">
         <v>61</v>
       </c>
-      <c r="E120" t="s">
+      <c r="G120" t="s">
         <v>150</v>
       </c>
-      <c r="F120" t="s">
+      <c r="H120" t="s">
         <v>580</v>
       </c>
-      <c r="G120" t="s">
+      <c r="I120" t="s">
         <v>581</v>
       </c>
-      <c r="H120" s="2">
+      <c r="J120" s="2">
         <v>3</v>
       </c>
-      <c r="I120" t="s">
+      <c r="K120" t="s">
         <v>582</v>
       </c>
-      <c r="J120" s="2">
+      <c r="L120" s="2">
         <v>1</v>
       </c>
-      <c r="K120" t="s">
+      <c r="M120" t="s">
         <v>328</v>
       </c>
-      <c r="L120" s="2">
+      <c r="N120" s="2">
         <v>2</v>
       </c>
-      <c r="M120" s="12" t="s">
+      <c r="O120" s="12" t="s">
         <v>2686</v>
-      </c>
-      <c r="N120" s="8" t="s">
-        <v>2548</v>
-      </c>
-      <c r="O120" s="8" t="s">
-        <v>2549</v>
       </c>
       <c r="P120" s="8" t="s">
         <v>2453</v>
@@ -22108,41 +22109,41 @@
       <c r="C121" t="s">
         <v>585</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="8" t="s">
+        <v>2550</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F121" t="s">
         <v>61</v>
       </c>
-      <c r="E121" t="s">
+      <c r="G121" t="s">
         <v>80</v>
       </c>
-      <c r="F121" t="s">
+      <c r="H121" t="s">
         <v>586</v>
       </c>
-      <c r="G121" t="s">
+      <c r="I121" t="s">
         <v>587</v>
       </c>
-      <c r="H121" s="2">
+      <c r="J121" s="2">
         <v>15</v>
       </c>
-      <c r="I121" t="s">
+      <c r="K121" t="s">
         <v>588</v>
       </c>
-      <c r="J121" s="2">
+      <c r="L121" s="2">
         <v>5</v>
       </c>
-      <c r="K121" t="s">
+      <c r="M121" t="s">
         <v>328</v>
       </c>
-      <c r="L121" s="2">
+      <c r="N121" s="2">
         <v>2</v>
       </c>
-      <c r="M121" s="12" t="s">
+      <c r="O121" s="12" t="s">
         <v>2687</v>
-      </c>
-      <c r="N121" s="8" t="s">
-        <v>2550</v>
-      </c>
-      <c r="O121" s="8" t="s">
-        <v>2407</v>
       </c>
       <c r="P121" s="8" t="s">
         <v>2425</v>
@@ -22158,41 +22159,41 @@
       <c r="C122" t="s">
         <v>590</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="8" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F122" t="s">
         <v>61</v>
       </c>
-      <c r="E122" t="s">
+      <c r="G122" t="s">
         <v>80</v>
       </c>
-      <c r="F122" t="s">
+      <c r="H122" t="s">
         <v>312</v>
       </c>
-      <c r="G122" t="s">
+      <c r="I122" t="s">
         <v>591</v>
       </c>
-      <c r="H122" s="2">
+      <c r="J122" s="2">
         <v>2</v>
       </c>
-      <c r="I122" t="s">
+      <c r="K122" t="s">
         <v>87</v>
       </c>
-      <c r="J122" s="2">
+      <c r="L122" s="2">
         <v>4</v>
       </c>
-      <c r="K122" t="s">
+      <c r="M122" t="s">
         <v>75</v>
       </c>
-      <c r="L122" s="2">
+      <c r="N122" s="2">
         <v>5</v>
       </c>
-      <c r="M122" s="12" t="s">
+      <c r="O122" s="12" t="s">
         <v>2688</v>
-      </c>
-      <c r="N122" s="8" t="s">
-        <v>2551</v>
-      </c>
-      <c r="O122" s="8" t="s">
-        <v>2407</v>
       </c>
       <c r="P122" s="8" t="s">
         <v>2552</v>
@@ -22208,41 +22209,41 @@
       <c r="C123" t="s">
         <v>593</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="8" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F123" t="s">
         <v>61</v>
       </c>
-      <c r="E123" t="s">
+      <c r="G123" t="s">
         <v>80</v>
       </c>
-      <c r="F123" t="s">
+      <c r="H123" t="s">
         <v>565</v>
       </c>
-      <c r="G123" t="s">
+      <c r="I123" t="s">
         <v>566</v>
       </c>
-      <c r="H123" s="2">
+      <c r="J123" s="2">
         <v>6</v>
       </c>
-      <c r="I123" t="s">
+      <c r="K123" t="s">
         <v>567</v>
       </c>
-      <c r="J123" s="2">
+      <c r="L123" s="2">
         <v>5</v>
       </c>
-      <c r="K123" t="s">
+      <c r="M123" t="s">
         <v>328</v>
       </c>
-      <c r="L123" s="2">
+      <c r="N123" s="2">
         <v>2</v>
       </c>
-      <c r="M123" s="12" t="s">
+      <c r="O123" s="12" t="s">
         <v>2689</v>
-      </c>
-      <c r="N123" s="8" t="s">
-        <v>2553</v>
-      </c>
-      <c r="O123" s="8" t="s">
-        <v>2407</v>
       </c>
       <c r="P123" s="8" t="s">
         <v>2552</v>
@@ -22258,26 +22259,26 @@
       <c r="C124" t="s">
         <v>596</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="8" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F124" t="s">
         <v>61</v>
       </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>150</v>
       </c>
-      <c r="F124" t="s">
+      <c r="H124" t="s">
         <v>597</v>
       </c>
-      <c r="G124" t="s">
+      <c r="I124" t="s">
         <v>598</v>
       </c>
-      <c r="H124" s="2">
+      <c r="J124" s="2">
         <v>1</v>
-      </c>
-      <c r="I124" t="s">
-        <v>48</v>
-      </c>
-      <c r="J124" s="2">
-        <v>0</v>
       </c>
       <c r="K124" t="s">
         <v>48</v>
@@ -22285,14 +22286,14 @@
       <c r="L124" s="2">
         <v>0</v>
       </c>
-      <c r="M124" s="12" t="s">
+      <c r="M124" t="s">
+        <v>48</v>
+      </c>
+      <c r="N124" s="2">
+        <v>0</v>
+      </c>
+      <c r="O124" s="12" t="s">
         <v>2690</v>
-      </c>
-      <c r="N124" s="8" t="s">
-        <v>2537</v>
-      </c>
-      <c r="O124" s="8" t="s">
-        <v>2538</v>
       </c>
       <c r="P124" s="8" t="s">
         <v>2415</v>
@@ -22308,41 +22309,41 @@
       <c r="C125" t="s">
         <v>600</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="8" t="s">
+        <v>2554</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F125" t="s">
         <v>61</v>
       </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>150</v>
       </c>
-      <c r="F125" t="s">
+      <c r="H125" t="s">
         <v>601</v>
       </c>
-      <c r="G125" t="s">
+      <c r="I125" t="s">
         <v>602</v>
-      </c>
-      <c r="H125" s="2">
-        <v>1</v>
-      </c>
-      <c r="I125" t="s">
-        <v>603</v>
       </c>
       <c r="J125" s="2">
         <v>1</v>
       </c>
       <c r="K125" t="s">
+        <v>603</v>
+      </c>
+      <c r="L125" s="2">
+        <v>1</v>
+      </c>
+      <c r="M125" t="s">
         <v>48</v>
       </c>
-      <c r="L125" s="2">
+      <c r="N125" s="2">
         <v>0</v>
       </c>
-      <c r="M125" s="12" t="s">
+      <c r="O125" s="12" t="s">
         <v>2691</v>
-      </c>
-      <c r="N125" s="8" t="s">
-        <v>2554</v>
-      </c>
-      <c r="O125" s="8" t="s">
-        <v>2538</v>
       </c>
       <c r="P125" s="8" t="s">
         <v>2415</v>
@@ -22358,41 +22359,41 @@
       <c r="C126" t="s">
         <v>605</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="8" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F126" t="s">
         <v>61</v>
       </c>
-      <c r="E126" t="s">
+      <c r="G126" t="s">
         <v>150</v>
       </c>
-      <c r="F126" t="s">
+      <c r="H126" t="s">
         <v>606</v>
       </c>
-      <c r="G126" t="s">
+      <c r="I126" t="s">
         <v>607</v>
-      </c>
-      <c r="H126" s="2">
-        <v>1</v>
-      </c>
-      <c r="I126" t="s">
-        <v>608</v>
       </c>
       <c r="J126" s="2">
         <v>1</v>
       </c>
       <c r="K126" t="s">
+        <v>608</v>
+      </c>
+      <c r="L126" s="2">
+        <v>1</v>
+      </c>
+      <c r="M126" t="s">
         <v>609</v>
       </c>
-      <c r="L126" s="2">
+      <c r="N126" s="2">
         <v>2</v>
       </c>
-      <c r="M126" s="12" t="s">
+      <c r="O126" s="12" t="s">
         <v>2692</v>
-      </c>
-      <c r="N126" s="8" t="s">
-        <v>2555</v>
-      </c>
-      <c r="O126" s="8" t="s">
-        <v>2538</v>
       </c>
       <c r="P126" s="8" t="s">
         <v>2415</v>
@@ -22408,41 +22409,41 @@
       <c r="C127" t="s">
         <v>611</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="8" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F127" t="s">
         <v>61</v>
       </c>
-      <c r="E127" t="s">
+      <c r="G127" t="s">
         <v>150</v>
       </c>
-      <c r="F127" t="s">
+      <c r="H127" t="s">
         <v>612</v>
       </c>
-      <c r="G127" t="s">
+      <c r="I127" t="s">
         <v>613</v>
-      </c>
-      <c r="H127" s="2">
-        <v>1</v>
-      </c>
-      <c r="I127" t="s">
-        <v>614</v>
       </c>
       <c r="J127" s="2">
         <v>1</v>
       </c>
       <c r="K127" t="s">
+        <v>614</v>
+      </c>
+      <c r="L127" s="2">
+        <v>1</v>
+      </c>
+      <c r="M127" t="s">
         <v>48</v>
       </c>
-      <c r="L127" s="2">
+      <c r="N127" s="2">
         <v>0</v>
       </c>
-      <c r="M127" s="12" t="s">
+      <c r="O127" s="12" t="s">
         <v>2693</v>
-      </c>
-      <c r="N127" s="8" t="s">
-        <v>2556</v>
-      </c>
-      <c r="O127" s="8" t="s">
-        <v>2538</v>
       </c>
       <c r="P127" s="8" t="s">
         <v>2415</v>
@@ -22458,40 +22459,40 @@
       <c r="C128" t="s">
         <v>617</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="8" t="s">
+        <v>2557</v>
+      </c>
+      <c r="E128" s="8"/>
+      <c r="F128" t="s">
         <v>61</v>
       </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>183</v>
       </c>
-      <c r="F128" t="s">
+      <c r="H128" t="s">
         <v>618</v>
       </c>
-      <c r="G128" t="s">
+      <c r="I128" t="s">
         <v>619</v>
-      </c>
-      <c r="H128" s="2">
-        <v>3</v>
-      </c>
-      <c r="I128" t="s">
-        <v>577</v>
       </c>
       <c r="J128" s="2">
         <v>3</v>
       </c>
       <c r="K128" t="s">
+        <v>577</v>
+      </c>
+      <c r="L128" s="2">
+        <v>3</v>
+      </c>
+      <c r="M128" t="s">
         <v>609</v>
       </c>
-      <c r="L128" s="2">
+      <c r="N128" s="2">
         <v>2</v>
       </c>
-      <c r="M128" s="12" t="s">
+      <c r="O128" s="12" t="s">
         <v>2694</v>
       </c>
-      <c r="N128" s="8" t="s">
-        <v>2557</v>
-      </c>
-      <c r="O128" s="8"/>
       <c r="P128" s="8" t="s">
         <v>2415</v>
       </c>
@@ -22506,41 +22507,41 @@
       <c r="C129" t="s">
         <v>622</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="8" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F129" t="s">
         <v>61</v>
       </c>
-      <c r="E129" t="s">
+      <c r="G129" t="s">
         <v>285</v>
       </c>
-      <c r="F129" t="s">
+      <c r="H129" t="s">
         <v>623</v>
       </c>
-      <c r="G129" t="s">
+      <c r="I129" t="s">
         <v>624</v>
       </c>
-      <c r="H129" s="2">
+      <c r="J129" s="2">
         <v>1</v>
       </c>
-      <c r="I129" t="s">
+      <c r="K129" t="s">
         <v>625</v>
       </c>
-      <c r="J129" s="2">
+      <c r="L129" s="2">
         <v>3</v>
       </c>
-      <c r="K129" t="s">
+      <c r="M129" t="s">
         <v>48</v>
       </c>
-      <c r="L129" s="2">
+      <c r="N129" s="2">
         <v>0</v>
       </c>
-      <c r="M129" s="12" t="s">
+      <c r="O129" s="12" t="s">
         <v>2695</v>
-      </c>
-      <c r="N129" s="8" t="s">
-        <v>2558</v>
-      </c>
-      <c r="O129" s="8" t="s">
-        <v>2408</v>
       </c>
       <c r="P129" s="8" t="s">
         <v>2552</v>
@@ -22556,41 +22557,41 @@
       <c r="C130" t="s">
         <v>627</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="8" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F130" t="s">
         <v>61</v>
       </c>
-      <c r="E130" t="s">
+      <c r="G130" t="s">
         <v>96</v>
       </c>
-      <c r="F130" t="s">
+      <c r="H130" t="s">
         <v>628</v>
       </c>
-      <c r="G130" t="s">
+      <c r="I130" t="s">
         <v>629</v>
-      </c>
-      <c r="H130" s="2">
-        <v>1</v>
-      </c>
-      <c r="I130" t="s">
-        <v>630</v>
       </c>
       <c r="J130" s="2">
         <v>1</v>
       </c>
       <c r="K130" t="s">
+        <v>630</v>
+      </c>
+      <c r="L130" s="2">
+        <v>1</v>
+      </c>
+      <c r="M130" t="s">
         <v>48</v>
       </c>
-      <c r="L130" s="2">
+      <c r="N130" s="2">
         <v>0</v>
       </c>
-      <c r="M130" s="12" t="s">
+      <c r="O130" s="12" t="s">
         <v>2696</v>
-      </c>
-      <c r="N130" s="8" t="s">
-        <v>2559</v>
-      </c>
-      <c r="O130" s="8" t="s">
-        <v>2408</v>
       </c>
       <c r="P130" s="8" t="s">
         <v>2560</v>
@@ -22606,41 +22607,41 @@
       <c r="C131" t="s">
         <v>632</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="8" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F131" t="s">
         <v>61</v>
       </c>
-      <c r="E131" t="s">
+      <c r="G131" t="s">
         <v>483</v>
       </c>
-      <c r="F131" t="s">
+      <c r="H131" t="s">
         <v>633</v>
       </c>
-      <c r="G131" t="s">
+      <c r="I131" t="s">
         <v>634</v>
       </c>
-      <c r="H131" s="2">
+      <c r="J131" s="2">
         <v>3</v>
       </c>
-      <c r="I131" t="s">
+      <c r="K131" t="s">
         <v>635</v>
       </c>
-      <c r="J131" s="2">
+      <c r="L131" s="2">
         <v>1</v>
       </c>
-      <c r="K131" t="s">
+      <c r="M131" t="s">
         <v>328</v>
       </c>
-      <c r="L131" s="2">
+      <c r="N131" s="2">
         <v>2</v>
       </c>
-      <c r="M131" s="12" t="s">
+      <c r="O131" s="12" t="s">
         <v>2697</v>
-      </c>
-      <c r="N131" s="8" t="s">
-        <v>2561</v>
-      </c>
-      <c r="O131" s="8" t="s">
-        <v>2408</v>
       </c>
       <c r="P131" s="8" t="s">
         <v>2453</v>
@@ -22656,20 +22657,18 @@
       <c r="C132" t="s">
         <v>638</v>
       </c>
-      <c r="D132" t="s">
-        <v>48</v>
-      </c>
-      <c r="E132" t="s">
-        <v>96</v>
-      </c>
+      <c r="D132" s="8" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E132" s="8"/>
       <c r="F132" t="s">
         <v>48</v>
       </c>
       <c r="G132" t="s">
+        <v>96</v>
+      </c>
+      <c r="H132" t="s">
         <v>48</v>
-      </c>
-      <c r="H132" s="2">
-        <v>0</v>
       </c>
       <c r="I132" t="s">
         <v>48</v>
@@ -22683,13 +22682,15 @@
       <c r="L132" s="2">
         <v>0</v>
       </c>
-      <c r="M132" s="12" t="s">
+      <c r="M132" t="s">
+        <v>48</v>
+      </c>
+      <c r="N132" s="2">
+        <v>0</v>
+      </c>
+      <c r="O132" s="12" t="s">
         <v>2698</v>
       </c>
-      <c r="N132" s="8" t="s">
-        <v>2562</v>
-      </c>
-      <c r="O132" s="8"/>
       <c r="P132" s="8" t="s">
         <v>2419</v>
       </c>
@@ -22704,20 +22705,18 @@
       <c r="C133" t="s">
         <v>640</v>
       </c>
-      <c r="D133" t="s">
-        <v>48</v>
-      </c>
-      <c r="E133" t="s">
-        <v>96</v>
-      </c>
+      <c r="D133" s="8" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E133" s="8"/>
       <c r="F133" t="s">
         <v>48</v>
       </c>
       <c r="G133" t="s">
+        <v>96</v>
+      </c>
+      <c r="H133" t="s">
         <v>48</v>
-      </c>
-      <c r="H133" s="2">
-        <v>0</v>
       </c>
       <c r="I133" t="s">
         <v>48</v>
@@ -22731,13 +22730,15 @@
       <c r="L133" s="2">
         <v>0</v>
       </c>
-      <c r="M133" s="12" t="s">
+      <c r="M133" t="s">
+        <v>48</v>
+      </c>
+      <c r="N133" s="2">
+        <v>0</v>
+      </c>
+      <c r="O133" s="12" t="s">
         <v>2699</v>
       </c>
-      <c r="N133" s="8" t="s">
-        <v>2562</v>
-      </c>
-      <c r="O133" s="8"/>
       <c r="P133" s="8" t="s">
         <v>2416</v>
       </c>
@@ -22752,20 +22753,18 @@
       <c r="C134" t="s">
         <v>642</v>
       </c>
-      <c r="D134" t="s">
-        <v>48</v>
-      </c>
-      <c r="E134" t="s">
-        <v>96</v>
-      </c>
+      <c r="D134" s="8" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E134" s="8"/>
       <c r="F134" t="s">
         <v>48</v>
       </c>
       <c r="G134" t="s">
+        <v>96</v>
+      </c>
+      <c r="H134" t="s">
         <v>48</v>
-      </c>
-      <c r="H134" s="2">
-        <v>0</v>
       </c>
       <c r="I134" t="s">
         <v>48</v>
@@ -22779,13 +22778,15 @@
       <c r="L134" s="2">
         <v>0</v>
       </c>
-      <c r="M134" s="12" t="s">
+      <c r="M134" t="s">
+        <v>48</v>
+      </c>
+      <c r="N134" s="2">
+        <v>0</v>
+      </c>
+      <c r="O134" s="12" t="s">
         <v>2700</v>
       </c>
-      <c r="N134" s="8" t="s">
-        <v>2562</v>
-      </c>
-      <c r="O134" s="8"/>
       <c r="P134" s="8" t="s">
         <v>2419</v>
       </c>
@@ -22800,20 +22801,18 @@
       <c r="C135" t="s">
         <v>645</v>
       </c>
-      <c r="D135" t="s">
-        <v>48</v>
-      </c>
-      <c r="E135" t="s">
-        <v>646</v>
-      </c>
+      <c r="D135" s="8" t="s">
+        <v>2563</v>
+      </c>
+      <c r="E135" s="8"/>
       <c r="F135" t="s">
         <v>48</v>
       </c>
       <c r="G135" t="s">
+        <v>646</v>
+      </c>
+      <c r="H135" t="s">
         <v>48</v>
-      </c>
-      <c r="H135" s="2">
-        <v>0</v>
       </c>
       <c r="I135" t="s">
         <v>48</v>
@@ -22827,13 +22826,15 @@
       <c r="L135" s="2">
         <v>0</v>
       </c>
-      <c r="M135" s="12" t="s">
+      <c r="M135" t="s">
+        <v>48</v>
+      </c>
+      <c r="N135" s="2">
+        <v>0</v>
+      </c>
+      <c r="O135" s="12" t="s">
         <v>2701</v>
       </c>
-      <c r="N135" s="8" t="s">
-        <v>2563</v>
-      </c>
-      <c r="O135" s="8"/>
       <c r="P135" s="8" t="s">
         <v>2419</v>
       </c>
@@ -22848,20 +22849,18 @@
       <c r="C136" t="s">
         <v>648</v>
       </c>
-      <c r="D136" t="s">
-        <v>48</v>
-      </c>
-      <c r="E136" t="s">
-        <v>646</v>
-      </c>
+      <c r="D136" s="8" t="s">
+        <v>2564</v>
+      </c>
+      <c r="E136" s="8"/>
       <c r="F136" t="s">
         <v>48</v>
       </c>
       <c r="G136" t="s">
+        <v>646</v>
+      </c>
+      <c r="H136" t="s">
         <v>48</v>
-      </c>
-      <c r="H136" s="2">
-        <v>0</v>
       </c>
       <c r="I136" t="s">
         <v>48</v>
@@ -22875,13 +22874,15 @@
       <c r="L136" s="2">
         <v>0</v>
       </c>
-      <c r="M136" s="12" t="s">
+      <c r="M136" t="s">
+        <v>48</v>
+      </c>
+      <c r="N136" s="2">
+        <v>0</v>
+      </c>
+      <c r="O136" s="12" t="s">
         <v>2702</v>
       </c>
-      <c r="N136" s="8" t="s">
-        <v>2564</v>
-      </c>
-      <c r="O136" s="8"/>
       <c r="P136" s="8" t="s">
         <v>2465</v>
       </c>
@@ -22896,20 +22897,18 @@
       <c r="C137" t="s">
         <v>651</v>
       </c>
-      <c r="D137" t="s">
-        <v>48</v>
-      </c>
-      <c r="E137" t="s">
-        <v>652</v>
-      </c>
+      <c r="D137" s="8" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E137" s="8"/>
       <c r="F137" t="s">
         <v>48</v>
       </c>
       <c r="G137" t="s">
+        <v>652</v>
+      </c>
+      <c r="H137" t="s">
         <v>48</v>
-      </c>
-      <c r="H137" s="2">
-        <v>0</v>
       </c>
       <c r="I137" t="s">
         <v>48</v>
@@ -22923,13 +22922,15 @@
       <c r="L137" s="2">
         <v>0</v>
       </c>
-      <c r="M137" s="12" t="s">
+      <c r="M137" t="s">
+        <v>48</v>
+      </c>
+      <c r="N137" s="2">
+        <v>0</v>
+      </c>
+      <c r="O137" s="12" t="s">
         <v>2703</v>
       </c>
-      <c r="N137" s="8" t="s">
-        <v>2565</v>
-      </c>
-      <c r="O137" s="8"/>
       <c r="P137" s="8" t="s">
         <v>2566</v>
       </c>
@@ -22944,20 +22945,18 @@
       <c r="C138" t="s">
         <v>654</v>
       </c>
-      <c r="D138" t="s">
-        <v>48</v>
-      </c>
-      <c r="E138" t="s">
-        <v>652</v>
-      </c>
+      <c r="D138" s="8" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E138" s="8"/>
       <c r="F138" t="s">
         <v>48</v>
       </c>
       <c r="G138" t="s">
+        <v>652</v>
+      </c>
+      <c r="H138" t="s">
         <v>48</v>
-      </c>
-      <c r="H138" s="2">
-        <v>0</v>
       </c>
       <c r="I138" t="s">
         <v>48</v>
@@ -22971,13 +22970,15 @@
       <c r="L138" s="2">
         <v>0</v>
       </c>
-      <c r="M138" s="12" t="s">
+      <c r="M138" t="s">
+        <v>48</v>
+      </c>
+      <c r="N138" s="2">
+        <v>0</v>
+      </c>
+      <c r="O138" s="12" t="s">
         <v>2704</v>
       </c>
-      <c r="N138" s="8" t="s">
-        <v>2536</v>
-      </c>
-      <c r="O138" s="8"/>
       <c r="P138" s="8" t="s">
         <v>2566</v>
       </c>
@@ -22992,20 +22993,18 @@
       <c r="C139" t="s">
         <v>656</v>
       </c>
-      <c r="D139" t="s">
-        <v>48</v>
-      </c>
-      <c r="E139" t="s">
-        <v>96</v>
-      </c>
+      <c r="D139" s="8" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E139" s="8"/>
       <c r="F139" t="s">
         <v>48</v>
       </c>
       <c r="G139" t="s">
+        <v>96</v>
+      </c>
+      <c r="H139" t="s">
         <v>48</v>
-      </c>
-      <c r="H139" s="2">
-        <v>0</v>
       </c>
       <c r="I139" t="s">
         <v>48</v>
@@ -23019,13 +23018,15 @@
       <c r="L139" s="2">
         <v>0</v>
       </c>
-      <c r="M139" s="12" t="s">
+      <c r="M139" t="s">
+        <v>48</v>
+      </c>
+      <c r="N139" s="2">
+        <v>0</v>
+      </c>
+      <c r="O139" s="12" t="s">
         <v>2705</v>
       </c>
-      <c r="N139" s="8" t="s">
-        <v>2567</v>
-      </c>
-      <c r="O139" s="8"/>
       <c r="P139" s="8" t="s">
         <v>2419</v>
       </c>
@@ -23040,20 +23041,18 @@
       <c r="C140" t="s">
         <v>659</v>
       </c>
-      <c r="D140" t="s">
-        <v>48</v>
-      </c>
-      <c r="E140" t="s">
-        <v>80</v>
-      </c>
+      <c r="D140" s="8" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E140" s="8"/>
       <c r="F140" t="s">
         <v>48</v>
       </c>
       <c r="G140" t="s">
+        <v>80</v>
+      </c>
+      <c r="H140" t="s">
         <v>48</v>
-      </c>
-      <c r="H140" s="2">
-        <v>0</v>
       </c>
       <c r="I140" t="s">
         <v>48</v>
@@ -23067,13 +23066,15 @@
       <c r="L140" s="2">
         <v>0</v>
       </c>
-      <c r="M140" s="12" t="s">
+      <c r="M140" t="s">
+        <v>48</v>
+      </c>
+      <c r="N140" s="2">
+        <v>0</v>
+      </c>
+      <c r="O140" s="12" t="s">
         <v>2706</v>
       </c>
-      <c r="N140" s="8" t="s">
-        <v>2568</v>
-      </c>
-      <c r="O140" s="8"/>
       <c r="P140" s="8" t="s">
         <v>2465</v>
       </c>
@@ -23088,20 +23089,18 @@
       <c r="C141" t="s">
         <v>661</v>
       </c>
-      <c r="D141" t="s">
-        <v>48</v>
-      </c>
-      <c r="E141" t="s">
-        <v>80</v>
-      </c>
+      <c r="D141" s="8" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E141" s="8"/>
       <c r="F141" t="s">
         <v>48</v>
       </c>
       <c r="G141" t="s">
+        <v>80</v>
+      </c>
+      <c r="H141" t="s">
         <v>48</v>
-      </c>
-      <c r="H141" s="2">
-        <v>0</v>
       </c>
       <c r="I141" t="s">
         <v>48</v>
@@ -23115,13 +23114,15 @@
       <c r="L141" s="2">
         <v>0</v>
       </c>
-      <c r="M141" s="12" t="s">
+      <c r="M141" t="s">
+        <v>48</v>
+      </c>
+      <c r="N141" s="2">
+        <v>0</v>
+      </c>
+      <c r="O141" s="12" t="s">
         <v>2707</v>
       </c>
-      <c r="N141" s="8" t="s">
-        <v>2568</v>
-      </c>
-      <c r="O141" s="8"/>
       <c r="P141" s="8" t="s">
         <v>2465</v>
       </c>

--- a/bjts/附录D-功能表程序血缘矩阵.xlsx
+++ b/bjts/附录D-功能表程序血缘矩阵.xlsx
@@ -16165,7 +16165,7 @@
         <v>2571</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="101">
+    <row r="2" spans="1:16" ht="171">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -17159,7 +17159,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="44">
+    <row r="22" spans="1:16" ht="72">
       <c r="A22" t="s">
         <v>133</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>2447</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="44">
+    <row r="23" spans="1:16" ht="72">
       <c r="A23" t="s">
         <v>140</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>2447</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="56">
+    <row r="24" spans="1:16" ht="72">
       <c r="A24" t="s">
         <v>142</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>2409</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="44">
+    <row r="26" spans="1:16" ht="72">
       <c r="A26" t="s">
         <v>154</v>
       </c>
@@ -17759,7 +17759,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="42">
+    <row r="34" spans="1:16" ht="43">
       <c r="A34" t="s">
         <v>192</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="29">
+    <row r="36" spans="1:16" ht="43">
       <c r="A36" t="s">
         <v>196</v>
       </c>
@@ -17909,7 +17909,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="29">
+    <row r="37" spans="1:16" ht="43">
       <c r="A37" t="s">
         <v>198</v>
       </c>
@@ -18607,7 +18607,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="44">
+    <row r="51" spans="1:16" ht="86">
       <c r="A51" t="s">
         <v>258</v>
       </c>
@@ -18657,7 +18657,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="84">
+    <row r="52" spans="1:16" ht="86">
       <c r="A52" t="s">
         <v>264</v>
       </c>
@@ -18707,7 +18707,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="56">
+    <row r="53" spans="1:16" ht="86">
       <c r="A53" t="s">
         <v>266</v>
       </c>
@@ -18757,7 +18757,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="44">
+    <row r="54" spans="1:16" ht="86">
       <c r="A54" t="s">
         <v>268</v>
       </c>
@@ -18807,7 +18807,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="44">
+    <row r="55" spans="1:16" ht="86">
       <c r="A55" t="s">
         <v>270</v>
       </c>
@@ -18857,7 +18857,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="44">
+    <row r="56" spans="1:16" ht="86">
       <c r="A56" t="s">
         <v>272</v>
       </c>
@@ -18907,7 +18907,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="56">
+    <row r="57" spans="1:16" ht="86">
       <c r="A57" t="s">
         <v>277</v>
       </c>
@@ -18957,7 +18957,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="29">
+    <row r="58" spans="1:16" ht="43">
       <c r="A58" t="s">
         <v>282</v>
       </c>
@@ -19007,7 +19007,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="42">
+    <row r="59" spans="1:16" ht="43">
       <c r="A59" t="s">
         <v>288</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="29">
+    <row r="60" spans="1:16" ht="43">
       <c r="A60" t="s">
         <v>292</v>
       </c>
@@ -19107,7 +19107,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="117">
+    <row r="61" spans="1:16" ht="187">
       <c r="A61" t="s">
         <v>294</v>
       </c>
@@ -19857,7 +19857,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="99">
+    <row r="76" spans="1:16" ht="155">
       <c r="A76" t="s">
         <v>363</v>
       </c>
@@ -19907,7 +19907,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="242">
+    <row r="77" spans="1:16" ht="409.5">
       <c r="A77" t="s">
         <v>370</v>
       </c>
@@ -19957,7 +19957,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="242">
+    <row r="78" spans="1:16" ht="409.5">
       <c r="A78" t="s">
         <v>374</v>
       </c>
@@ -20007,7 +20007,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="242">
+    <row r="79" spans="1:16" ht="409.5">
       <c r="A79" t="s">
         <v>379</v>
       </c>
@@ -20057,7 +20057,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="242">
+    <row r="80" spans="1:16" ht="409.5">
       <c r="A80" t="s">
         <v>385</v>
       </c>
@@ -20107,7 +20107,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="242">
+    <row r="81" spans="1:16" ht="409.5">
       <c r="A81" t="s">
         <v>390</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="242">
+    <row r="82" spans="1:16" ht="409.5">
       <c r="A82" t="s">
         <v>395</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="242">
+    <row r="83" spans="1:16" ht="409.5">
       <c r="A83" t="s">
         <v>400</v>
       </c>
@@ -20257,7 +20257,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="242">
+    <row r="84" spans="1:16" ht="409.5">
       <c r="A84" t="s">
         <v>405</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="242">
+    <row r="85" spans="1:16" ht="409.5">
       <c r="A85" t="s">
         <v>411</v>
       </c>
@@ -20357,7 +20357,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="242">
+    <row r="86" spans="1:16" ht="409.5">
       <c r="A86" t="s">
         <v>416</v>
       </c>
@@ -20407,7 +20407,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="242">
+    <row r="87" spans="1:16" ht="409.5">
       <c r="A87" t="s">
         <v>420</v>
       </c>
@@ -20457,7 +20457,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="242">
+    <row r="88" spans="1:16" ht="409.5">
       <c r="A88" t="s">
         <v>427</v>
       </c>
@@ -20657,7 +20657,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="30">
+    <row r="92" spans="1:16" ht="57">
       <c r="A92" t="s">
         <v>449</v>
       </c>
@@ -20807,7 +20807,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="56">
+    <row r="95" spans="1:16" ht="57">
       <c r="A95" t="s">
         <v>463</v>
       </c>
@@ -21007,7 +21007,7 @@
         <v>2413</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="29">
+    <row r="99" spans="1:16" ht="57">
       <c r="A99" t="s">
         <v>486</v>
       </c>
@@ -21057,7 +21057,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="29">
+    <row r="100" spans="1:16" ht="57">
       <c r="A100" t="s">
         <v>488</v>
       </c>
@@ -21307,7 +21307,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="43">
+    <row r="105" spans="1:16" ht="57">
       <c r="A105" t="s">
         <v>513</v>
       </c>
@@ -21599,7 +21599,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="189">
+    <row r="111" spans="1:16" ht="318">
       <c r="A111" t="s">
         <v>536</v>
       </c>
@@ -21649,7 +21649,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="43">
+    <row r="112" spans="1:16" ht="57">
       <c r="A112" t="s">
         <v>538</v>
       </c>
@@ -21799,7 +21799,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="257">
+    <row r="115" spans="1:16" ht="409.5">
       <c r="A115" t="s">
         <v>551</v>
       </c>
@@ -21849,7 +21849,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="257">
+    <row r="116" spans="1:16" ht="409.5">
       <c r="A116" t="s">
         <v>557</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="257">
+    <row r="117" spans="1:16" ht="409.5">
       <c r="A117" t="s">
         <v>563</v>
       </c>
@@ -21949,7 +21949,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="257">
+    <row r="118" spans="1:16" ht="409.5">
       <c r="A118" t="s">
         <v>568</v>
       </c>
@@ -21999,7 +21999,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="257">
+    <row r="119" spans="1:16" ht="409.5">
       <c r="A119" t="s">
         <v>573</v>
       </c>
@@ -22049,7 +22049,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="170">
+    <row r="120" spans="1:16" ht="296">
       <c r="A120" t="s">
         <v>578</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="43">
+    <row r="122" spans="1:16" ht="57">
       <c r="A122" t="s">
         <v>589</v>
       </c>
@@ -22199,7 +22199,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="43">
+    <row r="123" spans="1:16" ht="57">
       <c r="A123" t="s">
         <v>592</v>
       </c>
@@ -22249,7 +22249,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="189">
+    <row r="124" spans="1:16" ht="318">
       <c r="A124" t="s">
         <v>594</v>
       </c>
@@ -22299,7 +22299,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="189">
+    <row r="125" spans="1:16" ht="318">
       <c r="A125" t="s">
         <v>599</v>
       </c>
@@ -22349,7 +22349,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="226">
+    <row r="126" spans="1:16" ht="318">
       <c r="A126" t="s">
         <v>604</v>
       </c>
@@ -22399,7 +22399,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="189">
+    <row r="127" spans="1:16" ht="318">
       <c r="A127" t="s">
         <v>610</v>
       </c>
@@ -22497,7 +22497,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="99">
+    <row r="129" spans="1:16" ht="183">
       <c r="A129" t="s">
         <v>620</v>
       </c>
@@ -22547,7 +22547,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="99">
+    <row r="130" spans="1:16" ht="183">
       <c r="A130" t="s">
         <v>626</v>
       </c>
@@ -22597,7 +22597,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="115">
+    <row r="131" spans="1:16" ht="183">
       <c r="A131" t="s">
         <v>631</v>
       </c>
